--- a/스케쥴 시트/★★이게진짜 Daily 종합사이트 스케줄★★.xlsx
+++ b/스케쥴 시트/★★이게진짜 Daily 종합사이트 스케줄★★.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\정동교\문서 자동화 TEST\커서 바이브코딩 자동화 관련\스케쥴 시트\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75781CD-4116-4275-9FE8-2B6E0F9D8BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6462421D-C65C-4718-BF6F-8E96A09809ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1940,7 +1940,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2166,9 +2166,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2201,15 +2198,18 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2218,9 +2218,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2839,7 +2836,7 @@
   <cols>
     <col min="1" max="1" width="4.375" style="56" customWidth="1"/>
     <col min="2" max="7" width="25.625" style="56" customWidth="1"/>
-    <col min="8" max="8" width="25.625" style="67" customWidth="1"/>
+    <col min="8" max="8" width="25.625" style="65" customWidth="1"/>
     <col min="9" max="9" width="9" style="56"/>
     <col min="10" max="14" width="15.625" style="56" customWidth="1"/>
     <col min="15" max="15" width="34.25" style="56" customWidth="1"/>
@@ -2850,7 +2847,7 @@
     <col min="20" max="20" width="109.625" style="56" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="22.875" style="56" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10.125" style="56" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.625" style="67" customWidth="1"/>
+    <col min="23" max="24" width="14.625" style="65" customWidth="1"/>
     <col min="25" max="25" width="12" style="56" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="10.625" style="56" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="14.625" style="56" bestFit="1" customWidth="1"/>
@@ -2904,15 +2901,15 @@
     </row>
     <row r="2" spans="1:28" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="54"/>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
       <c r="I2" s="54"/>
       <c r="J2" s="54"/>
       <c r="K2" s="54"/>
@@ -2958,43 +2955,43 @@
         <v>7</v>
       </c>
       <c r="I3" s="54"/>
-      <c r="J3" s="58" t="s">
+      <c r="J3" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="59" t="s">
+      <c r="K3" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="59"/>
-      <c r="M3" s="59"/>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60" t="s">
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="Q3" s="60" t="s">
+      <c r="Q3" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="R3" s="61" t="s">
+      <c r="R3" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="S3" s="61" t="s">
+      <c r="S3" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="T3" s="61" t="s">
+      <c r="T3" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="U3" s="62" t="s">
+      <c r="U3" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="V3" s="62" t="s">
+      <c r="V3" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="66"/>
       <c r="Y3" s="54"/>
       <c r="Z3" s="54"/>
       <c r="AA3" s="54"/>
-      <c r="AB3" s="61" t="s">
+      <c r="AB3" s="60" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4642,15 +4639,15 @@
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A34" s="54"/>
-      <c r="B34" s="73" t="s">
+      <c r="B34" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="C34" s="74"/>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="75"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="74"/>
       <c r="I34" s="54"/>
       <c r="J34" s="9">
         <v>45973</v>
@@ -4694,13 +4691,13 @@
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A35" s="54"/>
-      <c r="B35" s="76"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="78"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="77"/>
       <c r="I35" s="54"/>
       <c r="J35" s="9">
         <v>45974</v>
@@ -4744,13 +4741,13 @@
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" s="54"/>
-      <c r="B36" s="76"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="78"/>
+      <c r="B36" s="75"/>
+      <c r="C36" s="76"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="77"/>
       <c r="I36" s="54"/>
       <c r="J36" s="9">
         <v>45974</v>
@@ -4792,13 +4789,13 @@
     </row>
     <row r="37" spans="1:28" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="54"/>
-      <c r="B37" s="79"/>
-      <c r="C37" s="80"/>
-      <c r="D37" s="80"/>
-      <c r="E37" s="80"/>
-      <c r="F37" s="80"/>
-      <c r="G37" s="80"/>
-      <c r="H37" s="81"/>
+      <c r="B37" s="78"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="80"/>
       <c r="I37" s="54"/>
       <c r="J37" s="9">
         <v>45974</v>
@@ -5310,15 +5307,15 @@
     </row>
     <row r="49" spans="1:28" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="54"/>
-      <c r="B49" s="83" t="s">
+      <c r="B49" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="C49" s="83"/>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="83"/>
+      <c r="C49" s="82"/>
+      <c r="D49" s="82"/>
+      <c r="E49" s="82"/>
+      <c r="F49" s="82"/>
+      <c r="G49" s="82"/>
+      <c r="H49" s="82"/>
       <c r="I49" s="54"/>
       <c r="J49" s="54"/>
       <c r="K49" s="54"/>
@@ -5364,43 +5361,43 @@
         <v>7</v>
       </c>
       <c r="I50" s="54"/>
-      <c r="J50" s="58" t="s">
+      <c r="J50" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="K50" s="59" t="s">
+      <c r="K50" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="L50" s="59"/>
-      <c r="M50" s="59"/>
-      <c r="N50" s="59"/>
-      <c r="O50" s="59"/>
-      <c r="P50" s="60" t="s">
+      <c r="L50" s="58"/>
+      <c r="M50" s="58"/>
+      <c r="N50" s="58"/>
+      <c r="O50" s="58"/>
+      <c r="P50" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="Q50" s="60" t="s">
+      <c r="Q50" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="R50" s="61" t="s">
+      <c r="R50" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="S50" s="61" t="s">
+      <c r="S50" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="T50" s="61" t="s">
+      <c r="T50" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="U50" s="62" t="s">
+      <c r="U50" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="V50" s="62" t="s">
+      <c r="V50" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="W50" s="68"/>
-      <c r="X50" s="68"/>
+      <c r="W50" s="66"/>
+      <c r="X50" s="66"/>
       <c r="Y50" s="54"/>
       <c r="Z50" s="54"/>
       <c r="AA50" s="54"/>
-      <c r="AB50" s="61" t="s">
+      <c r="AB50" s="60" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7068,15 +7065,15 @@
     </row>
     <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81" s="54"/>
-      <c r="B81" s="73" t="s">
+      <c r="B81" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="C81" s="74"/>
-      <c r="D81" s="74"/>
-      <c r="E81" s="74"/>
-      <c r="F81" s="74"/>
-      <c r="G81" s="74"/>
-      <c r="H81" s="75"/>
+      <c r="C81" s="73"/>
+      <c r="D81" s="73"/>
+      <c r="E81" s="73"/>
+      <c r="F81" s="73"/>
+      <c r="G81" s="73"/>
+      <c r="H81" s="74"/>
       <c r="I81" s="54"/>
       <c r="J81" s="9">
         <v>46001</v>
@@ -7120,13 +7117,13 @@
     </row>
     <row r="82" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A82" s="54"/>
-      <c r="B82" s="76"/>
-      <c r="C82" s="77"/>
-      <c r="D82" s="77"/>
-      <c r="E82" s="77"/>
-      <c r="F82" s="77"/>
-      <c r="G82" s="77"/>
-      <c r="H82" s="78"/>
+      <c r="B82" s="75"/>
+      <c r="C82" s="76"/>
+      <c r="D82" s="76"/>
+      <c r="E82" s="76"/>
+      <c r="F82" s="76"/>
+      <c r="G82" s="76"/>
+      <c r="H82" s="77"/>
       <c r="I82" s="54"/>
       <c r="J82" s="9">
         <v>46001</v>
@@ -7170,13 +7167,13 @@
     </row>
     <row r="83" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A83" s="54"/>
-      <c r="B83" s="76"/>
-      <c r="C83" s="77"/>
-      <c r="D83" s="77"/>
-      <c r="E83" s="77"/>
-      <c r="F83" s="77"/>
-      <c r="G83" s="77"/>
-      <c r="H83" s="78"/>
+      <c r="B83" s="75"/>
+      <c r="C83" s="76"/>
+      <c r="D83" s="76"/>
+      <c r="E83" s="76"/>
+      <c r="F83" s="76"/>
+      <c r="G83" s="76"/>
+      <c r="H83" s="77"/>
       <c r="I83" s="54"/>
       <c r="J83" s="9">
         <v>46001</v>
@@ -7220,13 +7217,13 @@
     </row>
     <row r="84" spans="1:28" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="54"/>
-      <c r="B84" s="79"/>
-      <c r="C84" s="80"/>
-      <c r="D84" s="80"/>
-      <c r="E84" s="80"/>
-      <c r="F84" s="80"/>
-      <c r="G84" s="80"/>
-      <c r="H84" s="81"/>
+      <c r="B84" s="78"/>
+      <c r="C84" s="79"/>
+      <c r="D84" s="79"/>
+      <c r="E84" s="79"/>
+      <c r="F84" s="79"/>
+      <c r="G84" s="79"/>
+      <c r="H84" s="80"/>
       <c r="I84" s="54"/>
       <c r="J84" s="9">
         <v>46001</v>
@@ -7596,17 +7593,17 @@
     </row>
     <row r="92" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="54"/>
-      <c r="B92" s="82" t="s">
+      <c r="B92" s="81" t="s">
         <v>137</v>
       </c>
-      <c r="C92" s="82"/>
-      <c r="D92" s="82"/>
-      <c r="E92" s="82"/>
-      <c r="F92" s="82"/>
+      <c r="C92" s="81"/>
+      <c r="D92" s="81"/>
+      <c r="E92" s="81"/>
+      <c r="F92" s="81"/>
       <c r="G92" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="H92" s="63">
+      <c r="H92" s="62">
         <f>IFERROR(COUNTIFS(L94:L134, "&lt;&gt;", M94:M134, "", N94:N134, "") / COUNTA(L94:L134), 0)</f>
         <v>0.75</v>
       </c>
@@ -7655,10 +7652,10 @@
         <v>7</v>
       </c>
       <c r="I93" s="54"/>
-      <c r="J93" s="58" t="s">
+      <c r="J93" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="K93" s="59" t="s">
+      <c r="K93" s="58" t="s">
         <v>21</v>
       </c>
       <c r="L93" s="51" t="s">
@@ -7673,33 +7670,33 @@
       <c r="O93" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="P93" s="60" t="s">
+      <c r="P93" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="Q93" s="60" t="s">
+      <c r="Q93" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="R93" s="61" t="s">
+      <c r="R93" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="S93" s="61" t="s">
+      <c r="S93" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="T93" s="61" t="s">
+      <c r="T93" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="U93" s="62" t="s">
+      <c r="U93" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="V93" s="62" t="s">
+      <c r="V93" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="W93" s="68"/>
-      <c r="X93" s="68"/>
+      <c r="W93" s="66"/>
+      <c r="X93" s="66"/>
       <c r="Y93" s="54"/>
       <c r="Z93" s="54"/>
       <c r="AA93" s="54"/>
-      <c r="AB93" s="61" t="s">
+      <c r="AB93" s="60" t="s">
         <v>27</v>
       </c>
     </row>
@@ -9363,15 +9360,15 @@
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A124" s="54"/>
-      <c r="B124" s="73" t="s">
+      <c r="B124" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="C124" s="74"/>
-      <c r="D124" s="74"/>
-      <c r="E124" s="74"/>
-      <c r="F124" s="74"/>
-      <c r="G124" s="74"/>
-      <c r="H124" s="75"/>
+      <c r="C124" s="73"/>
+      <c r="D124" s="73"/>
+      <c r="E124" s="73"/>
+      <c r="F124" s="73"/>
+      <c r="G124" s="73"/>
+      <c r="H124" s="74"/>
       <c r="I124" s="54"/>
       <c r="J124" s="9">
         <v>46041</v>
@@ -9415,13 +9412,13 @@
     </row>
     <row r="125" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A125" s="54"/>
-      <c r="B125" s="76"/>
-      <c r="C125" s="77"/>
-      <c r="D125" s="77"/>
-      <c r="E125" s="77"/>
-      <c r="F125" s="77"/>
-      <c r="G125" s="77"/>
-      <c r="H125" s="78"/>
+      <c r="B125" s="75"/>
+      <c r="C125" s="76"/>
+      <c r="D125" s="76"/>
+      <c r="E125" s="76"/>
+      <c r="F125" s="76"/>
+      <c r="G125" s="76"/>
+      <c r="H125" s="77"/>
       <c r="I125" s="54"/>
       <c r="J125" s="9">
         <v>46041</v>
@@ -9465,13 +9462,13 @@
     </row>
     <row r="126" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A126" s="54"/>
-      <c r="B126" s="76"/>
-      <c r="C126" s="77"/>
-      <c r="D126" s="77"/>
-      <c r="E126" s="77"/>
-      <c r="F126" s="77"/>
-      <c r="G126" s="77"/>
-      <c r="H126" s="78"/>
+      <c r="B126" s="75"/>
+      <c r="C126" s="76"/>
+      <c r="D126" s="76"/>
+      <c r="E126" s="76"/>
+      <c r="F126" s="76"/>
+      <c r="G126" s="76"/>
+      <c r="H126" s="77"/>
       <c r="I126" s="54"/>
       <c r="J126" s="9">
         <v>46041</v>
@@ -9515,13 +9512,13 @@
     </row>
     <row r="127" spans="1:28" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="54"/>
-      <c r="B127" s="79"/>
-      <c r="C127" s="80"/>
-      <c r="D127" s="80"/>
-      <c r="E127" s="80"/>
-      <c r="F127" s="80"/>
-      <c r="G127" s="80"/>
-      <c r="H127" s="81"/>
+      <c r="B127" s="78"/>
+      <c r="C127" s="79"/>
+      <c r="D127" s="79"/>
+      <c r="E127" s="79"/>
+      <c r="F127" s="79"/>
+      <c r="G127" s="79"/>
+      <c r="H127" s="80"/>
       <c r="I127" s="54"/>
       <c r="J127" s="9">
         <v>46034</v>
@@ -9890,23 +9887,23 @@
       <c r="AB135" s="45"/>
     </row>
     <row r="136" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A136" s="64"/>
-      <c r="B136" s="64"/>
-      <c r="C136" s="64"/>
-      <c r="D136" s="64"/>
-      <c r="E136" s="64"/>
-      <c r="F136" s="64"/>
-      <c r="G136" s="64"/>
+      <c r="A136" s="63"/>
+      <c r="B136" s="63"/>
+      <c r="C136" s="63"/>
+      <c r="D136" s="63"/>
+      <c r="E136" s="63"/>
+      <c r="F136" s="63"/>
+      <c r="G136" s="63"/>
       <c r="H136" s="52"/>
-      <c r="I136" s="64"/>
-      <c r="J136" s="64"/>
-      <c r="K136" s="64"/>
-      <c r="L136" s="64"/>
-      <c r="M136" s="64"/>
-      <c r="N136" s="64"/>
-      <c r="O136" s="64"/>
-      <c r="P136" s="64"/>
-      <c r="Q136" s="64"/>
+      <c r="I136" s="63"/>
+      <c r="J136" s="63"/>
+      <c r="K136" s="63"/>
+      <c r="L136" s="63"/>
+      <c r="M136" s="63"/>
+      <c r="N136" s="63"/>
+      <c r="O136" s="63"/>
+      <c r="P136" s="63"/>
+      <c r="Q136" s="63"/>
       <c r="R136" s="52"/>
       <c r="S136" s="52"/>
       <c r="T136" s="52"/>
@@ -9951,17 +9948,17 @@
     </row>
     <row r="138" spans="1:29" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="54"/>
-      <c r="B138" s="82" t="s">
+      <c r="B138" s="81" t="s">
         <v>182</v>
       </c>
-      <c r="C138" s="82"/>
-      <c r="D138" s="82"/>
-      <c r="E138" s="82"/>
-      <c r="F138" s="82"/>
+      <c r="C138" s="81"/>
+      <c r="D138" s="81"/>
+      <c r="E138" s="81"/>
+      <c r="F138" s="81"/>
       <c r="G138" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="H138" s="63">
+      <c r="H138" s="62">
         <f>IFERROR(COUNTIFS(L140:L180, "&lt;&gt;", M140:M180, "", N140:N180, "") / COUNTA(L140:L180), 0)</f>
         <v>0</v>
       </c>
@@ -10010,10 +10007,10 @@
         <v>7</v>
       </c>
       <c r="I139" s="54"/>
-      <c r="J139" s="58" t="s">
+      <c r="J139" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="K139" s="59" t="s">
+      <c r="K139" s="58" t="s">
         <v>21</v>
       </c>
       <c r="L139" s="51" t="s">
@@ -10028,42 +10025,42 @@
       <c r="O139" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="P139" s="60" t="s">
+      <c r="P139" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="Q139" s="60" t="s">
+      <c r="Q139" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="R139" s="61" t="s">
+      <c r="R139" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="S139" s="61" t="s">
+      <c r="S139" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="T139" s="61" t="s">
+      <c r="T139" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="U139" s="62" t="s">
+      <c r="U139" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="V139" s="62" t="s">
+      <c r="V139" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="W139" s="65"/>
-      <c r="X139" s="65"/>
-      <c r="Y139" s="61" t="s">
+      <c r="W139" s="64"/>
+      <c r="X139" s="64"/>
+      <c r="Y139" s="60" t="s">
         <v>312</v>
       </c>
-      <c r="Z139" s="61" t="s">
+      <c r="Z139" s="60" t="s">
         <v>313</v>
       </c>
-      <c r="AA139" s="61" t="s">
+      <c r="AA139" s="60" t="s">
         <v>314</v>
       </c>
-      <c r="AB139" s="65" t="s">
+      <c r="AB139" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="AC139" s="66" t="s">
+      <c r="AC139" s="67" t="s">
         <v>316</v>
       </c>
     </row>
@@ -10130,7 +10127,7 @@
       <c r="AB140" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC140" s="57"/>
+      <c r="AC140" s="68"/>
     </row>
     <row r="141" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A141" s="54"/>
@@ -10191,7 +10188,7 @@
       <c r="AB141" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC141" s="57"/>
+      <c r="AC141" s="68"/>
     </row>
     <row r="142" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A142" s="54"/>
@@ -10248,7 +10245,7 @@
       <c r="AB142" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC142" s="57"/>
+      <c r="AC142" s="68"/>
     </row>
     <row r="143" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A143" s="54"/>
@@ -10295,7 +10292,7 @@
       <c r="AB143" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC143" s="57"/>
+      <c r="AC143" s="68"/>
     </row>
     <row r="144" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A144" s="54"/>
@@ -10344,7 +10341,7 @@
       <c r="AB144" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC144" s="57"/>
+      <c r="AC144" s="68"/>
     </row>
     <row r="145" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A145" s="54"/>
@@ -10405,7 +10402,7 @@
       <c r="AB145" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC145" s="57"/>
+      <c r="AC145" s="68"/>
     </row>
     <row r="146" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A146" s="54"/>
@@ -10462,7 +10459,7 @@
       <c r="AB146" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC146" s="57"/>
+      <c r="AC146" s="68"/>
     </row>
     <row r="147" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A147" s="54"/>
@@ -10521,7 +10518,7 @@
       <c r="AB147" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC147" s="57"/>
+      <c r="AC147" s="68"/>
     </row>
     <row r="148" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A148" s="54"/>
@@ -10576,7 +10573,7 @@
       <c r="AB148" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC148" s="57"/>
+      <c r="AC148" s="68"/>
     </row>
     <row r="149" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A149" s="54"/>
@@ -10629,7 +10626,7 @@
       <c r="AB149" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC149" s="57"/>
+      <c r="AC149" s="68"/>
     </row>
     <row r="150" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A150" s="54"/>
@@ -10694,7 +10691,7 @@
       <c r="AB150" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC150" s="57"/>
+      <c r="AC150" s="68"/>
     </row>
     <row r="151" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A151" s="54"/>
@@ -10745,7 +10742,7 @@
       <c r="AB151" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC151" s="57"/>
+      <c r="AC151" s="68"/>
     </row>
     <row r="152" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A152" s="54"/>
@@ -10796,7 +10793,7 @@
       <c r="AB152" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC152" s="57"/>
+      <c r="AC152" s="68"/>
     </row>
     <row r="153" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A153" s="54"/>
@@ -10847,7 +10844,7 @@
       <c r="AB153" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC153" s="57"/>
+      <c r="AC153" s="68"/>
     </row>
     <row r="154" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A154" s="54"/>
@@ -10900,7 +10897,7 @@
       <c r="AB154" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC154" s="57"/>
+      <c r="AC154" s="68"/>
     </row>
     <row r="155" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A155" s="54"/>
@@ -10965,7 +10962,7 @@
       <c r="AB155" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC155" s="57"/>
+      <c r="AC155" s="68"/>
     </row>
     <row r="156" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A156" s="54"/>
@@ -11024,7 +11021,7 @@
       <c r="AB156" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC156" s="57"/>
+      <c r="AC156" s="68"/>
     </row>
     <row r="157" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A157" s="54"/>
@@ -11079,7 +11076,7 @@
       <c r="AB157" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC157" s="57"/>
+      <c r="AC157" s="68"/>
     </row>
     <row r="158" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A158" s="54"/>
@@ -11132,7 +11129,7 @@
       <c r="AB158" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC158" s="57"/>
+      <c r="AC158" s="68"/>
     </row>
     <row r="159" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A159" s="54"/>
@@ -11185,7 +11182,7 @@
       <c r="AB159" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC159" s="57"/>
+      <c r="AC159" s="68"/>
     </row>
     <row r="160" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A160" s="54"/>
@@ -11236,7 +11233,7 @@
       <c r="AB160" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC160" s="57"/>
+      <c r="AC160" s="68"/>
     </row>
     <row r="161" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A161" s="54"/>
@@ -11287,7 +11284,7 @@
       <c r="AB161" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC161" s="57"/>
+      <c r="AC161" s="68"/>
     </row>
     <row r="162" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A162" s="54"/>
@@ -11338,7 +11335,7 @@
       <c r="AB162" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC162" s="57"/>
+      <c r="AC162" s="68"/>
     </row>
     <row r="163" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A163" s="54"/>
@@ -11389,7 +11386,7 @@
       <c r="AB163" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC163" s="57"/>
+      <c r="AC163" s="68"/>
     </row>
     <row r="164" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A164" s="54"/>
@@ -11440,7 +11437,7 @@
       <c r="AB164" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC164" s="57"/>
+      <c r="AC164" s="68"/>
     </row>
     <row r="165" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A165" s="54"/>
@@ -11491,7 +11488,7 @@
       <c r="AB165" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC165" s="57"/>
+      <c r="AC165" s="68"/>
     </row>
     <row r="166" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A166" s="54"/>
@@ -11542,7 +11539,7 @@
       <c r="AB166" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC166" s="57"/>
+      <c r="AC166" s="68"/>
     </row>
     <row r="167" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A167" s="54"/>
@@ -11593,7 +11590,7 @@
       <c r="AB167" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC167" s="57"/>
+      <c r="AC167" s="68"/>
     </row>
     <row r="168" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A168" s="54"/>
@@ -11644,7 +11641,7 @@
       <c r="AB168" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC168" s="57"/>
+      <c r="AC168" s="68"/>
     </row>
     <row r="169" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A169" s="54"/>
@@ -11695,19 +11692,19 @@
       <c r="AB169" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="AC169" s="57"/>
+      <c r="AC169" s="68"/>
     </row>
     <row r="170" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A170" s="54"/>
-      <c r="B170" s="73" t="s">
+      <c r="B170" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="C170" s="74"/>
-      <c r="D170" s="74"/>
-      <c r="E170" s="74"/>
-      <c r="F170" s="74"/>
-      <c r="G170" s="74"/>
-      <c r="H170" s="75"/>
+      <c r="C170" s="73"/>
+      <c r="D170" s="73"/>
+      <c r="E170" s="73"/>
+      <c r="F170" s="73"/>
+      <c r="G170" s="73"/>
+      <c r="H170" s="74"/>
       <c r="I170" s="54"/>
       <c r="J170" s="9">
         <v>46072</v>
@@ -11748,17 +11745,17 @@
       <c r="AB170" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC170" s="57"/>
+      <c r="AC170" s="68"/>
     </row>
     <row r="171" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A171" s="54"/>
-      <c r="B171" s="76"/>
-      <c r="C171" s="77"/>
-      <c r="D171" s="77"/>
-      <c r="E171" s="77"/>
-      <c r="F171" s="77"/>
-      <c r="G171" s="77"/>
-      <c r="H171" s="78"/>
+      <c r="B171" s="75"/>
+      <c r="C171" s="76"/>
+      <c r="D171" s="76"/>
+      <c r="E171" s="76"/>
+      <c r="F171" s="76"/>
+      <c r="G171" s="76"/>
+      <c r="H171" s="77"/>
       <c r="I171" s="54"/>
       <c r="J171" s="9">
         <v>46072</v>
@@ -11799,17 +11796,17 @@
       <c r="AB171" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC171" s="57"/>
+      <c r="AC171" s="68"/>
     </row>
     <row r="172" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A172" s="54"/>
-      <c r="B172" s="76"/>
-      <c r="C172" s="77"/>
-      <c r="D172" s="77"/>
-      <c r="E172" s="77"/>
-      <c r="F172" s="77"/>
-      <c r="G172" s="77"/>
-      <c r="H172" s="78"/>
+      <c r="B172" s="75"/>
+      <c r="C172" s="76"/>
+      <c r="D172" s="76"/>
+      <c r="E172" s="76"/>
+      <c r="F172" s="76"/>
+      <c r="G172" s="76"/>
+      <c r="H172" s="77"/>
       <c r="I172" s="54"/>
       <c r="J172" s="9">
         <v>46072</v>
@@ -11850,17 +11847,17 @@
       <c r="AB172" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC172" s="57"/>
+      <c r="AC172" s="68"/>
     </row>
     <row r="173" spans="1:29" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="54"/>
-      <c r="B173" s="79"/>
-      <c r="C173" s="80"/>
-      <c r="D173" s="80"/>
-      <c r="E173" s="80"/>
-      <c r="F173" s="80"/>
-      <c r="G173" s="80"/>
-      <c r="H173" s="81"/>
+      <c r="B173" s="78"/>
+      <c r="C173" s="79"/>
+      <c r="D173" s="79"/>
+      <c r="E173" s="79"/>
+      <c r="F173" s="79"/>
+      <c r="G173" s="79"/>
+      <c r="H173" s="80"/>
       <c r="I173" s="54"/>
       <c r="J173" s="9"/>
       <c r="K173" s="10"/>
@@ -11883,7 +11880,7 @@
       <c r="AB173" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC173" s="57"/>
+      <c r="AC173" s="68"/>
     </row>
     <row r="174" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A174" s="54"/>
@@ -11916,7 +11913,7 @@
       <c r="AB174" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC174" s="57"/>
+      <c r="AC174" s="68"/>
     </row>
     <row r="175" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A175" s="54"/>
@@ -11949,7 +11946,7 @@
       <c r="AB175" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC175" s="57"/>
+      <c r="AC175" s="68"/>
     </row>
     <row r="176" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A176" s="54"/>
@@ -11982,7 +11979,7 @@
       <c r="AB176" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC176" s="57"/>
+      <c r="AC176" s="68"/>
     </row>
     <row r="177" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A177" s="54"/>
@@ -12015,7 +12012,7 @@
       <c r="AB177" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC177" s="57"/>
+      <c r="AC177" s="68"/>
     </row>
     <row r="178" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A178" s="54"/>
@@ -12048,7 +12045,7 @@
       <c r="AB178" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC178" s="57"/>
+      <c r="AC178" s="68"/>
     </row>
     <row r="179" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A179" s="54"/>
@@ -12081,7 +12078,7 @@
       <c r="AB179" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC179" s="57"/>
+      <c r="AC179" s="68"/>
     </row>
     <row r="180" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A180" s="54"/>
@@ -12114,26 +12111,26 @@
       <c r="AB180" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="AC180" s="57"/>
+      <c r="AC180" s="68"/>
     </row>
     <row r="181" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A181" s="64"/>
-      <c r="B181" s="64"/>
-      <c r="C181" s="64"/>
-      <c r="D181" s="64"/>
-      <c r="E181" s="64"/>
-      <c r="F181" s="64"/>
-      <c r="G181" s="64"/>
+      <c r="A181" s="63"/>
+      <c r="B181" s="63"/>
+      <c r="C181" s="63"/>
+      <c r="D181" s="63"/>
+      <c r="E181" s="63"/>
+      <c r="F181" s="63"/>
+      <c r="G181" s="63"/>
       <c r="H181" s="52"/>
-      <c r="I181" s="64"/>
-      <c r="J181" s="64"/>
-      <c r="K181" s="64"/>
-      <c r="L181" s="64"/>
-      <c r="M181" s="64"/>
-      <c r="N181" s="64"/>
-      <c r="O181" s="64"/>
-      <c r="P181" s="64"/>
-      <c r="Q181" s="64"/>
+      <c r="I181" s="63"/>
+      <c r="J181" s="63"/>
+      <c r="K181" s="63"/>
+      <c r="L181" s="63"/>
+      <c r="M181" s="63"/>
+      <c r="N181" s="63"/>
+      <c r="O181" s="63"/>
+      <c r="P181" s="63"/>
+      <c r="Q181" s="63"/>
       <c r="R181" s="52"/>
       <c r="S181" s="52"/>
       <c r="T181" s="52"/>
@@ -12145,7 +12142,7 @@
       <c r="Z181" s="55"/>
       <c r="AA181" s="55"/>
       <c r="AB181" s="52"/>
-      <c r="AC181" s="57"/>
+      <c r="AC181" s="68"/>
     </row>
     <row r="182" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A182" s="54"/>
@@ -12179,17 +12176,17 @@
     </row>
     <row r="183" spans="1:29" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="54"/>
-      <c r="B183" s="82" t="s">
+      <c r="B183" s="81" t="s">
         <v>260</v>
       </c>
-      <c r="C183" s="82"/>
-      <c r="D183" s="82"/>
-      <c r="E183" s="82"/>
-      <c r="F183" s="82"/>
+      <c r="C183" s="81"/>
+      <c r="D183" s="81"/>
+      <c r="E183" s="81"/>
+      <c r="F183" s="81"/>
       <c r="G183" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="H183" s="63">
+      <c r="H183" s="62">
         <f>IFERROR(COUNTIFS(L185:L225, "&lt;&gt;", M185:M225, "", N185:N225, "") / COUNTA(L185:L225), 0)</f>
         <v>0.5</v>
       </c>
@@ -12238,10 +12235,10 @@
         <v>7</v>
       </c>
       <c r="I184" s="54"/>
-      <c r="J184" s="58" t="s">
+      <c r="J184" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="K184" s="59" t="s">
+      <c r="K184" s="58" t="s">
         <v>21</v>
       </c>
       <c r="L184" s="51" t="s">
@@ -12256,43 +12253,43 @@
       <c r="O184" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="P184" s="60" t="s">
+      <c r="P184" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="Q184" s="60" t="s">
+      <c r="Q184" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="R184" s="61" t="s">
+      <c r="R184" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="S184" s="61" t="s">
+      <c r="S184" s="60" t="s">
         <v>326</v>
       </c>
-      <c r="T184" s="61" t="s">
+      <c r="T184" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="U184" s="62" t="s">
+      <c r="U184" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="V184" s="62" t="s">
+      <c r="V184" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="W184" s="61" t="s">
+      <c r="W184" s="60" t="s">
         <v>329</v>
       </c>
-      <c r="X184" s="61" t="s">
+      <c r="X184" s="60" t="s">
         <v>331</v>
       </c>
-      <c r="Y184" s="61" t="s">
+      <c r="Y184" s="60" t="s">
         <v>327</v>
       </c>
-      <c r="Z184" s="61" t="s">
+      <c r="Z184" s="60" t="s">
         <v>330</v>
       </c>
-      <c r="AA184" s="61" t="s">
+      <c r="AA184" s="60" t="s">
         <v>328</v>
       </c>
-      <c r="AB184" s="61" t="s">
+      <c r="AB184" s="60" t="s">
         <v>27</v>
       </c>
       <c r="AC184" s="69" t="s">
@@ -12356,8 +12353,8 @@
       <c r="V185" s="14">
         <v>4</v>
       </c>
-      <c r="W185" s="72"/>
-      <c r="X185" s="72"/>
+      <c r="W185" s="13"/>
+      <c r="X185" s="13"/>
       <c r="Y185" s="55" t="s">
         <v>319</v>
       </c>
@@ -12423,10 +12420,10 @@
       <c r="V186" s="14">
         <v>3</v>
       </c>
-      <c r="W186" s="72" t="s">
+      <c r="W186" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="X186" s="72" t="s">
+      <c r="X186" s="13" t="s">
         <v>337</v>
       </c>
       <c r="Y186" s="55" t="s">
@@ -12468,8 +12465,8 @@
       <c r="T187" s="13"/>
       <c r="U187" s="13"/>
       <c r="V187" s="14"/>
-      <c r="W187" s="72"/>
-      <c r="X187" s="72"/>
+      <c r="W187" s="13"/>
+      <c r="X187" s="13"/>
       <c r="Y187" s="55"/>
       <c r="Z187" s="55"/>
       <c r="AA187" s="55"/>
@@ -12501,8 +12498,8 @@
       <c r="T188" s="13"/>
       <c r="U188" s="13"/>
       <c r="V188" s="14"/>
-      <c r="W188" s="72"/>
-      <c r="X188" s="72"/>
+      <c r="W188" s="13"/>
+      <c r="X188" s="13"/>
       <c r="Y188" s="55"/>
       <c r="Z188" s="55"/>
       <c r="AA188" s="55"/>
@@ -12534,8 +12531,8 @@
       <c r="T189" s="13"/>
       <c r="U189" s="13"/>
       <c r="V189" s="14"/>
-      <c r="W189" s="72"/>
-      <c r="X189" s="72"/>
+      <c r="W189" s="13"/>
+      <c r="X189" s="13"/>
       <c r="Y189" s="55"/>
       <c r="Z189" s="55"/>
       <c r="AA189" s="55"/>
@@ -12581,8 +12578,8 @@
       <c r="T190" s="13"/>
       <c r="U190" s="13"/>
       <c r="V190" s="14"/>
-      <c r="W190" s="72"/>
-      <c r="X190" s="72"/>
+      <c r="W190" s="13"/>
+      <c r="X190" s="13"/>
       <c r="Y190" s="55"/>
       <c r="Z190" s="55"/>
       <c r="AA190" s="55"/>
@@ -12616,8 +12613,8 @@
       <c r="T191" s="13"/>
       <c r="U191" s="13"/>
       <c r="V191" s="14"/>
-      <c r="W191" s="72"/>
-      <c r="X191" s="72"/>
+      <c r="W191" s="13"/>
+      <c r="X191" s="13"/>
       <c r="Y191" s="55"/>
       <c r="Z191" s="55"/>
       <c r="AA191" s="55"/>
@@ -12649,8 +12646,8 @@
       <c r="T192" s="13"/>
       <c r="U192" s="13"/>
       <c r="V192" s="14"/>
-      <c r="W192" s="72"/>
-      <c r="X192" s="72"/>
+      <c r="W192" s="13"/>
+      <c r="X192" s="13"/>
       <c r="Y192" s="55"/>
       <c r="Z192" s="55"/>
       <c r="AA192" s="55"/>
@@ -12682,8 +12679,8 @@
       <c r="T193" s="13"/>
       <c r="U193" s="13"/>
       <c r="V193" s="14"/>
-      <c r="W193" s="72"/>
-      <c r="X193" s="72"/>
+      <c r="W193" s="13"/>
+      <c r="X193" s="13"/>
       <c r="Y193" s="55"/>
       <c r="Z193" s="55"/>
       <c r="AA193" s="55"/>
@@ -12715,8 +12712,8 @@
       <c r="T194" s="13"/>
       <c r="U194" s="13"/>
       <c r="V194" s="14"/>
-      <c r="W194" s="72"/>
-      <c r="X194" s="72"/>
+      <c r="W194" s="13"/>
+      <c r="X194" s="13"/>
       <c r="Y194" s="55"/>
       <c r="Z194" s="55"/>
       <c r="AA194" s="55"/>
@@ -12762,8 +12759,8 @@
       <c r="T195" s="13"/>
       <c r="U195" s="13"/>
       <c r="V195" s="14"/>
-      <c r="W195" s="72"/>
-      <c r="X195" s="72"/>
+      <c r="W195" s="13"/>
+      <c r="X195" s="13"/>
       <c r="Y195" s="55"/>
       <c r="Z195" s="55"/>
       <c r="AA195" s="55"/>
@@ -12795,8 +12792,8 @@
       <c r="T196" s="13"/>
       <c r="U196" s="13"/>
       <c r="V196" s="14"/>
-      <c r="W196" s="72"/>
-      <c r="X196" s="72"/>
+      <c r="W196" s="13"/>
+      <c r="X196" s="13"/>
       <c r="Y196" s="55"/>
       <c r="Z196" s="55"/>
       <c r="AA196" s="55"/>
@@ -12828,8 +12825,8 @@
       <c r="T197" s="13"/>
       <c r="U197" s="13"/>
       <c r="V197" s="14"/>
-      <c r="W197" s="72"/>
-      <c r="X197" s="72"/>
+      <c r="W197" s="13"/>
+      <c r="X197" s="13"/>
       <c r="Y197" s="55"/>
       <c r="Z197" s="55"/>
       <c r="AA197" s="55"/>
@@ -12861,8 +12858,8 @@
       <c r="T198" s="13"/>
       <c r="U198" s="13"/>
       <c r="V198" s="14"/>
-      <c r="W198" s="72"/>
-      <c r="X198" s="72"/>
+      <c r="W198" s="13"/>
+      <c r="X198" s="13"/>
       <c r="Y198" s="55"/>
       <c r="Z198" s="55"/>
       <c r="AA198" s="55"/>
@@ -12894,8 +12891,8 @@
       <c r="T199" s="13"/>
       <c r="U199" s="13"/>
       <c r="V199" s="14"/>
-      <c r="W199" s="72"/>
-      <c r="X199" s="72"/>
+      <c r="W199" s="13"/>
+      <c r="X199" s="13"/>
       <c r="Y199" s="55"/>
       <c r="Z199" s="55"/>
       <c r="AA199" s="55"/>
@@ -12941,8 +12938,8 @@
       <c r="T200" s="13"/>
       <c r="U200" s="13"/>
       <c r="V200" s="14"/>
-      <c r="W200" s="72"/>
-      <c r="X200" s="72"/>
+      <c r="W200" s="13"/>
+      <c r="X200" s="13"/>
       <c r="Y200" s="55"/>
       <c r="Z200" s="55"/>
       <c r="AA200" s="55"/>
@@ -12978,8 +12975,8 @@
       <c r="T201" s="13"/>
       <c r="U201" s="13"/>
       <c r="V201" s="13"/>
-      <c r="W201" s="72"/>
-      <c r="X201" s="72"/>
+      <c r="W201" s="13"/>
+      <c r="X201" s="13"/>
       <c r="Y201" s="55"/>
       <c r="Z201" s="55"/>
       <c r="AA201" s="55"/>
@@ -13011,8 +13008,8 @@
       <c r="T202" s="13"/>
       <c r="U202" s="13"/>
       <c r="V202" s="13"/>
-      <c r="W202" s="72"/>
-      <c r="X202" s="72"/>
+      <c r="W202" s="13"/>
+      <c r="X202" s="13"/>
       <c r="Y202" s="55"/>
       <c r="Z202" s="55"/>
       <c r="AA202" s="55"/>
@@ -13044,8 +13041,8 @@
       <c r="T203" s="13"/>
       <c r="U203" s="13"/>
       <c r="V203" s="13"/>
-      <c r="W203" s="72"/>
-      <c r="X203" s="72"/>
+      <c r="W203" s="13"/>
+      <c r="X203" s="13"/>
       <c r="Y203" s="55"/>
       <c r="Z203" s="55"/>
       <c r="AA203" s="55"/>
@@ -13077,8 +13074,8 @@
       <c r="T204" s="13"/>
       <c r="U204" s="13"/>
       <c r="V204" s="13"/>
-      <c r="W204" s="72"/>
-      <c r="X204" s="72"/>
+      <c r="W204" s="13"/>
+      <c r="X204" s="13"/>
       <c r="Y204" s="55"/>
       <c r="Z204" s="55"/>
       <c r="AA204" s="55"/>
@@ -13116,8 +13113,8 @@
       <c r="T205" s="13"/>
       <c r="U205" s="13"/>
       <c r="V205" s="13"/>
-      <c r="W205" s="72"/>
-      <c r="X205" s="72"/>
+      <c r="W205" s="13"/>
+      <c r="X205" s="13"/>
       <c r="Y205" s="55"/>
       <c r="Z205" s="55"/>
       <c r="AA205" s="55"/>
@@ -13149,8 +13146,8 @@
       <c r="T206" s="13"/>
       <c r="U206" s="13"/>
       <c r="V206" s="14"/>
-      <c r="W206" s="72"/>
-      <c r="X206" s="72"/>
+      <c r="W206" s="13"/>
+      <c r="X206" s="13"/>
       <c r="Y206" s="55"/>
       <c r="Z206" s="55"/>
       <c r="AA206" s="55"/>
@@ -13182,8 +13179,8 @@
       <c r="T207" s="13"/>
       <c r="U207" s="13"/>
       <c r="V207" s="13"/>
-      <c r="W207" s="72"/>
-      <c r="X207" s="72"/>
+      <c r="W207" s="13"/>
+      <c r="X207" s="13"/>
       <c r="Y207" s="55"/>
       <c r="Z207" s="55"/>
       <c r="AA207" s="55"/>
@@ -13215,8 +13212,8 @@
       <c r="T208" s="13"/>
       <c r="U208" s="13"/>
       <c r="V208" s="13"/>
-      <c r="W208" s="72"/>
-      <c r="X208" s="72"/>
+      <c r="W208" s="13"/>
+      <c r="X208" s="13"/>
       <c r="Y208" s="55"/>
       <c r="Z208" s="55"/>
       <c r="AA208" s="55"/>
@@ -13248,8 +13245,8 @@
       <c r="T209" s="13"/>
       <c r="U209" s="13"/>
       <c r="V209" s="13"/>
-      <c r="W209" s="72"/>
-      <c r="X209" s="72"/>
+      <c r="W209" s="13"/>
+      <c r="X209" s="13"/>
       <c r="Y209" s="55"/>
       <c r="Z209" s="55"/>
       <c r="AA209" s="55"/>
@@ -13281,8 +13278,8 @@
       <c r="T210" s="13"/>
       <c r="U210" s="13"/>
       <c r="V210" s="14"/>
-      <c r="W210" s="72"/>
-      <c r="X210" s="72"/>
+      <c r="W210" s="13"/>
+      <c r="X210" s="13"/>
       <c r="Y210" s="55"/>
       <c r="Z210" s="55"/>
       <c r="AA210" s="55"/>
@@ -13314,8 +13311,8 @@
       <c r="T211" s="13"/>
       <c r="U211" s="13"/>
       <c r="V211" s="13"/>
-      <c r="W211" s="72"/>
-      <c r="X211" s="72"/>
+      <c r="W211" s="13"/>
+      <c r="X211" s="13"/>
       <c r="Y211" s="55"/>
       <c r="Z211" s="55"/>
       <c r="AA211" s="55"/>
@@ -13347,8 +13344,8 @@
       <c r="T212" s="13"/>
       <c r="U212" s="13"/>
       <c r="V212" s="13"/>
-      <c r="W212" s="72"/>
-      <c r="X212" s="72"/>
+      <c r="W212" s="13"/>
+      <c r="X212" s="13"/>
       <c r="Y212" s="55"/>
       <c r="Z212" s="55"/>
       <c r="AA212" s="55"/>
@@ -13380,8 +13377,8 @@
       <c r="T213" s="13"/>
       <c r="U213" s="13"/>
       <c r="V213" s="13"/>
-      <c r="W213" s="72"/>
-      <c r="X213" s="72"/>
+      <c r="W213" s="13"/>
+      <c r="X213" s="13"/>
       <c r="Y213" s="55"/>
       <c r="Z213" s="55"/>
       <c r="AA213" s="55"/>
@@ -13413,8 +13410,8 @@
       <c r="T214" s="13"/>
       <c r="U214" s="13"/>
       <c r="V214" s="13"/>
-      <c r="W214" s="72"/>
-      <c r="X214" s="72"/>
+      <c r="W214" s="13"/>
+      <c r="X214" s="13"/>
       <c r="Y214" s="55"/>
       <c r="Z214" s="55"/>
       <c r="AA214" s="55"/>
@@ -13425,15 +13422,15 @@
     </row>
     <row r="215" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A215" s="54"/>
-      <c r="B215" s="73" t="s">
+      <c r="B215" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="C215" s="74"/>
-      <c r="D215" s="74"/>
-      <c r="E215" s="74"/>
-      <c r="F215" s="74"/>
-      <c r="G215" s="74"/>
-      <c r="H215" s="75"/>
+      <c r="C215" s="73"/>
+      <c r="D215" s="73"/>
+      <c r="E215" s="73"/>
+      <c r="F215" s="73"/>
+      <c r="G215" s="73"/>
+      <c r="H215" s="74"/>
       <c r="I215" s="54"/>
       <c r="J215" s="9"/>
       <c r="K215" s="10"/>
@@ -13448,8 +13445,8 @@
       <c r="T215" s="13"/>
       <c r="U215" s="13"/>
       <c r="V215" s="13"/>
-      <c r="W215" s="72"/>
-      <c r="X215" s="72"/>
+      <c r="W215" s="13"/>
+      <c r="X215" s="13"/>
       <c r="Y215" s="55"/>
       <c r="Z215" s="55"/>
       <c r="AA215" s="55"/>
@@ -13460,13 +13457,13 @@
     </row>
     <row r="216" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A216" s="54"/>
-      <c r="B216" s="76"/>
-      <c r="C216" s="77"/>
-      <c r="D216" s="77"/>
-      <c r="E216" s="77"/>
-      <c r="F216" s="77"/>
-      <c r="G216" s="77"/>
-      <c r="H216" s="78"/>
+      <c r="B216" s="75"/>
+      <c r="C216" s="76"/>
+      <c r="D216" s="76"/>
+      <c r="E216" s="76"/>
+      <c r="F216" s="76"/>
+      <c r="G216" s="76"/>
+      <c r="H216" s="77"/>
       <c r="I216" s="54"/>
       <c r="J216" s="9"/>
       <c r="K216" s="10"/>
@@ -13481,8 +13478,8 @@
       <c r="T216" s="13"/>
       <c r="U216" s="13"/>
       <c r="V216" s="13"/>
-      <c r="W216" s="72"/>
-      <c r="X216" s="72"/>
+      <c r="W216" s="13"/>
+      <c r="X216" s="13"/>
       <c r="Y216" s="55"/>
       <c r="Z216" s="55"/>
       <c r="AA216" s="55"/>
@@ -13493,13 +13490,13 @@
     </row>
     <row r="217" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A217" s="54"/>
-      <c r="B217" s="76"/>
-      <c r="C217" s="77"/>
-      <c r="D217" s="77"/>
-      <c r="E217" s="77"/>
-      <c r="F217" s="77"/>
-      <c r="G217" s="77"/>
-      <c r="H217" s="78"/>
+      <c r="B217" s="75"/>
+      <c r="C217" s="76"/>
+      <c r="D217" s="76"/>
+      <c r="E217" s="76"/>
+      <c r="F217" s="76"/>
+      <c r="G217" s="76"/>
+      <c r="H217" s="77"/>
       <c r="I217" s="54"/>
       <c r="J217" s="9"/>
       <c r="K217" s="10"/>
@@ -13514,8 +13511,8 @@
       <c r="T217" s="13"/>
       <c r="U217" s="13"/>
       <c r="V217" s="13"/>
-      <c r="W217" s="72"/>
-      <c r="X217" s="72"/>
+      <c r="W217" s="13"/>
+      <c r="X217" s="13"/>
       <c r="Y217" s="55"/>
       <c r="Z217" s="55"/>
       <c r="AA217" s="55"/>
@@ -13526,13 +13523,13 @@
     </row>
     <row r="218" spans="1:29" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="54"/>
-      <c r="B218" s="79"/>
-      <c r="C218" s="80"/>
-      <c r="D218" s="80"/>
-      <c r="E218" s="80"/>
-      <c r="F218" s="80"/>
-      <c r="G218" s="80"/>
-      <c r="H218" s="81"/>
+      <c r="B218" s="78"/>
+      <c r="C218" s="79"/>
+      <c r="D218" s="79"/>
+      <c r="E218" s="79"/>
+      <c r="F218" s="79"/>
+      <c r="G218" s="79"/>
+      <c r="H218" s="80"/>
       <c r="I218" s="54"/>
       <c r="J218" s="9"/>
       <c r="K218" s="10"/>
@@ -13547,8 +13544,8 @@
       <c r="T218" s="13"/>
       <c r="U218" s="13"/>
       <c r="V218" s="13"/>
-      <c r="W218" s="72"/>
-      <c r="X218" s="72"/>
+      <c r="W218" s="13"/>
+      <c r="X218" s="13"/>
       <c r="Y218" s="55"/>
       <c r="Z218" s="55"/>
       <c r="AA218" s="55"/>
@@ -13580,8 +13577,8 @@
       <c r="T219" s="13"/>
       <c r="U219" s="13"/>
       <c r="V219" s="13"/>
-      <c r="W219" s="72"/>
-      <c r="X219" s="72"/>
+      <c r="W219" s="13"/>
+      <c r="X219" s="13"/>
       <c r="Y219" s="55"/>
       <c r="Z219" s="55"/>
       <c r="AA219" s="55"/>
@@ -13613,8 +13610,8 @@
       <c r="T220" s="13"/>
       <c r="U220" s="13"/>
       <c r="V220" s="13"/>
-      <c r="W220" s="72"/>
-      <c r="X220" s="72"/>
+      <c r="W220" s="13"/>
+      <c r="X220" s="13"/>
       <c r="Y220" s="55"/>
       <c r="Z220" s="55"/>
       <c r="AA220" s="55"/>
@@ -13646,8 +13643,8 @@
       <c r="T221" s="13"/>
       <c r="U221" s="13"/>
       <c r="V221" s="13"/>
-      <c r="W221" s="72"/>
-      <c r="X221" s="72"/>
+      <c r="W221" s="13"/>
+      <c r="X221" s="13"/>
       <c r="Y221" s="55"/>
       <c r="Z221" s="55"/>
       <c r="AA221" s="55"/>
@@ -13679,8 +13676,8 @@
       <c r="T222" s="13"/>
       <c r="U222" s="13"/>
       <c r="V222" s="13"/>
-      <c r="W222" s="72"/>
-      <c r="X222" s="72"/>
+      <c r="W222" s="13"/>
+      <c r="X222" s="13"/>
       <c r="Y222" s="55"/>
       <c r="Z222" s="55"/>
       <c r="AA222" s="55"/>
@@ -13712,8 +13709,8 @@
       <c r="T223" s="13"/>
       <c r="U223" s="13"/>
       <c r="V223" s="13"/>
-      <c r="W223" s="72"/>
-      <c r="X223" s="72"/>
+      <c r="W223" s="13"/>
+      <c r="X223" s="13"/>
       <c r="Y223" s="55"/>
       <c r="Z223" s="55"/>
       <c r="AA223" s="55"/>
@@ -13745,8 +13742,8 @@
       <c r="T224" s="13"/>
       <c r="U224" s="13"/>
       <c r="V224" s="13"/>
-      <c r="W224" s="72"/>
-      <c r="X224" s="72"/>
+      <c r="W224" s="13"/>
+      <c r="X224" s="13"/>
       <c r="Y224" s="55"/>
       <c r="Z224" s="55"/>
       <c r="AA224" s="55"/>
@@ -13778,8 +13775,8 @@
       <c r="T225" s="13"/>
       <c r="U225" s="13"/>
       <c r="V225" s="13"/>
-      <c r="W225" s="72"/>
-      <c r="X225" s="72"/>
+      <c r="W225" s="13"/>
+      <c r="X225" s="13"/>
       <c r="Y225" s="55"/>
       <c r="Z225" s="55"/>
       <c r="AA225" s="55"/>
@@ -13789,23 +13786,23 @@
       <c r="AC225" s="70"/>
     </row>
     <row r="226" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A226" s="64"/>
-      <c r="B226" s="64"/>
-      <c r="C226" s="64"/>
-      <c r="D226" s="64"/>
-      <c r="E226" s="64"/>
-      <c r="F226" s="64"/>
-      <c r="G226" s="64"/>
+      <c r="A226" s="63"/>
+      <c r="B226" s="63"/>
+      <c r="C226" s="63"/>
+      <c r="D226" s="63"/>
+      <c r="E226" s="63"/>
+      <c r="F226" s="63"/>
+      <c r="G226" s="63"/>
       <c r="H226" s="52"/>
-      <c r="I226" s="64"/>
-      <c r="J226" s="64"/>
-      <c r="K226" s="64"/>
-      <c r="L226" s="64"/>
-      <c r="M226" s="64"/>
-      <c r="N226" s="64"/>
-      <c r="O226" s="64"/>
-      <c r="P226" s="64"/>
-      <c r="Q226" s="64"/>
+      <c r="I226" s="63"/>
+      <c r="J226" s="63"/>
+      <c r="K226" s="63"/>
+      <c r="L226" s="63"/>
+      <c r="M226" s="63"/>
+      <c r="N226" s="63"/>
+      <c r="O226" s="63"/>
+      <c r="P226" s="63"/>
+      <c r="Q226" s="63"/>
       <c r="R226" s="52"/>
       <c r="S226" s="52"/>
       <c r="T226" s="52"/>
@@ -13851,17 +13848,17 @@
     </row>
     <row r="228" spans="1:29" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="54"/>
-      <c r="B228" s="82" t="s">
+      <c r="B228" s="81" t="s">
         <v>259</v>
       </c>
-      <c r="C228" s="82"/>
-      <c r="D228" s="82"/>
-      <c r="E228" s="82"/>
-      <c r="F228" s="82"/>
+      <c r="C228" s="81"/>
+      <c r="D228" s="81"/>
+      <c r="E228" s="81"/>
+      <c r="F228" s="81"/>
       <c r="G228" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="H228" s="63">
+      <c r="H228" s="62">
         <f>IFERROR(COUNTIFS(L230:L270, "&lt;&gt;", M230:M270, "", N230:N270, "") / COUNTA(L230:L270), 0)</f>
         <v>0</v>
       </c>
@@ -13910,10 +13907,10 @@
         <v>7</v>
       </c>
       <c r="I229" s="54"/>
-      <c r="J229" s="58" t="s">
+      <c r="J229" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="K229" s="59" t="s">
+      <c r="K229" s="58" t="s">
         <v>21</v>
       </c>
       <c r="L229" s="51" t="s">
@@ -13928,41 +13925,41 @@
       <c r="O229" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="P229" s="60" t="s">
+      <c r="P229" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="Q229" s="60" t="s">
+      <c r="Q229" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="R229" s="61" t="s">
+      <c r="R229" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="S229" s="61" t="s">
+      <c r="S229" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="T229" s="61" t="s">
+      <c r="T229" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="U229" s="62" t="s">
+      <c r="U229" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="V229" s="62" t="s">
+      <c r="V229" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="W229" s="61" t="s">
+      <c r="W229" s="60" t="s">
         <v>329</v>
       </c>
-      <c r="X229" s="61"/>
-      <c r="Y229" s="61" t="s">
+      <c r="X229" s="60"/>
+      <c r="Y229" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="Z229" s="61" t="s">
+      <c r="Z229" s="60" t="s">
         <v>313</v>
       </c>
-      <c r="AA229" s="61" t="s">
+      <c r="AA229" s="60" t="s">
         <v>325</v>
       </c>
-      <c r="AB229" s="61" t="s">
+      <c r="AB229" s="60" t="s">
         <v>27</v>
       </c>
       <c r="AC229" s="71" t="s">
@@ -14000,8 +13997,8 @@
       <c r="T230" s="13"/>
       <c r="U230" s="13"/>
       <c r="V230" s="14"/>
-      <c r="W230" s="72"/>
-      <c r="X230" s="72"/>
+      <c r="W230" s="13"/>
+      <c r="X230" s="13"/>
       <c r="Y230" s="55"/>
       <c r="Z230" s="55"/>
       <c r="AA230" s="55"/>
@@ -14033,8 +14030,8 @@
       <c r="T231" s="13"/>
       <c r="U231" s="13"/>
       <c r="V231" s="14"/>
-      <c r="W231" s="72"/>
-      <c r="X231" s="72"/>
+      <c r="W231" s="13"/>
+      <c r="X231" s="13"/>
       <c r="Y231" s="55"/>
       <c r="Z231" s="55"/>
       <c r="AA231" s="55"/>
@@ -14066,8 +14063,8 @@
       <c r="T232" s="13"/>
       <c r="U232" s="13"/>
       <c r="V232" s="14"/>
-      <c r="W232" s="72"/>
-      <c r="X232" s="72"/>
+      <c r="W232" s="13"/>
+      <c r="X232" s="13"/>
       <c r="Y232" s="55"/>
       <c r="Z232" s="55"/>
       <c r="AA232" s="55"/>
@@ -14099,8 +14096,8 @@
       <c r="T233" s="13"/>
       <c r="U233" s="13"/>
       <c r="V233" s="14"/>
-      <c r="W233" s="72"/>
-      <c r="X233" s="72"/>
+      <c r="W233" s="13"/>
+      <c r="X233" s="13"/>
       <c r="Y233" s="55"/>
       <c r="Z233" s="55"/>
       <c r="AA233" s="55"/>
@@ -14132,8 +14129,8 @@
       <c r="T234" s="13"/>
       <c r="U234" s="13"/>
       <c r="V234" s="14"/>
-      <c r="W234" s="72"/>
-      <c r="X234" s="72"/>
+      <c r="W234" s="13"/>
+      <c r="X234" s="13"/>
       <c r="Y234" s="55"/>
       <c r="Z234" s="55"/>
       <c r="AA234" s="55"/>
@@ -14179,8 +14176,8 @@
       <c r="T235" s="13"/>
       <c r="U235" s="13"/>
       <c r="V235" s="14"/>
-      <c r="W235" s="72"/>
-      <c r="X235" s="72"/>
+      <c r="W235" s="13"/>
+      <c r="X235" s="13"/>
       <c r="Y235" s="55"/>
       <c r="Z235" s="55"/>
       <c r="AA235" s="55"/>
@@ -14212,8 +14209,8 @@
       <c r="T236" s="13"/>
       <c r="U236" s="13"/>
       <c r="V236" s="14"/>
-      <c r="W236" s="72"/>
-      <c r="X236" s="72"/>
+      <c r="W236" s="13"/>
+      <c r="X236" s="13"/>
       <c r="Y236" s="55"/>
       <c r="Z236" s="55"/>
       <c r="AA236" s="55"/>
@@ -14245,8 +14242,8 @@
       <c r="T237" s="13"/>
       <c r="U237" s="13"/>
       <c r="V237" s="14"/>
-      <c r="W237" s="72"/>
-      <c r="X237" s="72"/>
+      <c r="W237" s="13"/>
+      <c r="X237" s="13"/>
       <c r="Y237" s="55"/>
       <c r="Z237" s="55"/>
       <c r="AA237" s="55"/>
@@ -14278,8 +14275,8 @@
       <c r="T238" s="13"/>
       <c r="U238" s="13"/>
       <c r="V238" s="14"/>
-      <c r="W238" s="72"/>
-      <c r="X238" s="72"/>
+      <c r="W238" s="13"/>
+      <c r="X238" s="13"/>
       <c r="Y238" s="55"/>
       <c r="Z238" s="55"/>
       <c r="AA238" s="55"/>
@@ -14311,8 +14308,8 @@
       <c r="T239" s="13"/>
       <c r="U239" s="13"/>
       <c r="V239" s="14"/>
-      <c r="W239" s="72"/>
-      <c r="X239" s="72"/>
+      <c r="W239" s="13"/>
+      <c r="X239" s="13"/>
       <c r="Y239" s="55"/>
       <c r="Z239" s="55"/>
       <c r="AA239" s="55"/>
@@ -14358,8 +14355,8 @@
       <c r="T240" s="13"/>
       <c r="U240" s="13"/>
       <c r="V240" s="14"/>
-      <c r="W240" s="72"/>
-      <c r="X240" s="72"/>
+      <c r="W240" s="13"/>
+      <c r="X240" s="13"/>
       <c r="Y240" s="55"/>
       <c r="Z240" s="55"/>
       <c r="AA240" s="55"/>
@@ -14391,8 +14388,8 @@
       <c r="T241" s="13"/>
       <c r="U241" s="13"/>
       <c r="V241" s="14"/>
-      <c r="W241" s="72"/>
-      <c r="X241" s="72"/>
+      <c r="W241" s="13"/>
+      <c r="X241" s="13"/>
       <c r="Y241" s="55"/>
       <c r="Z241" s="55"/>
       <c r="AA241" s="55"/>
@@ -14424,8 +14421,8 @@
       <c r="T242" s="13"/>
       <c r="U242" s="13"/>
       <c r="V242" s="14"/>
-      <c r="W242" s="72"/>
-      <c r="X242" s="72"/>
+      <c r="W242" s="13"/>
+      <c r="X242" s="13"/>
       <c r="Y242" s="55"/>
       <c r="Z242" s="55"/>
       <c r="AA242" s="55"/>
@@ -14457,8 +14454,8 @@
       <c r="T243" s="13"/>
       <c r="U243" s="13"/>
       <c r="V243" s="14"/>
-      <c r="W243" s="72"/>
-      <c r="X243" s="72"/>
+      <c r="W243" s="13"/>
+      <c r="X243" s="13"/>
       <c r="Y243" s="55"/>
       <c r="Z243" s="55"/>
       <c r="AA243" s="55"/>
@@ -14490,8 +14487,8 @@
       <c r="T244" s="13"/>
       <c r="U244" s="13"/>
       <c r="V244" s="14"/>
-      <c r="W244" s="72"/>
-      <c r="X244" s="72"/>
+      <c r="W244" s="13"/>
+      <c r="X244" s="13"/>
       <c r="Y244" s="55"/>
       <c r="Z244" s="55"/>
       <c r="AA244" s="55"/>
@@ -14537,8 +14534,8 @@
       <c r="T245" s="13"/>
       <c r="U245" s="13"/>
       <c r="V245" s="14"/>
-      <c r="W245" s="72"/>
-      <c r="X245" s="72"/>
+      <c r="W245" s="13"/>
+      <c r="X245" s="13"/>
       <c r="Y245" s="55"/>
       <c r="Z245" s="55"/>
       <c r="AA245" s="55"/>
@@ -14570,8 +14567,8 @@
       <c r="T246" s="13"/>
       <c r="U246" s="13"/>
       <c r="V246" s="13"/>
-      <c r="W246" s="72"/>
-      <c r="X246" s="72"/>
+      <c r="W246" s="13"/>
+      <c r="X246" s="13"/>
       <c r="Y246" s="55"/>
       <c r="Z246" s="55"/>
       <c r="AA246" s="55"/>
@@ -14603,8 +14600,8 @@
       <c r="T247" s="13"/>
       <c r="U247" s="13"/>
       <c r="V247" s="13"/>
-      <c r="W247" s="72"/>
-      <c r="X247" s="72"/>
+      <c r="W247" s="13"/>
+      <c r="X247" s="13"/>
       <c r="Y247" s="55"/>
       <c r="Z247" s="55"/>
       <c r="AA247" s="55"/>
@@ -14636,8 +14633,8 @@
       <c r="T248" s="13"/>
       <c r="U248" s="13"/>
       <c r="V248" s="13"/>
-      <c r="W248" s="72"/>
-      <c r="X248" s="72"/>
+      <c r="W248" s="13"/>
+      <c r="X248" s="13"/>
       <c r="Y248" s="55"/>
       <c r="Z248" s="55"/>
       <c r="AA248" s="55"/>
@@ -14669,8 +14666,8 @@
       <c r="T249" s="13"/>
       <c r="U249" s="13"/>
       <c r="V249" s="13"/>
-      <c r="W249" s="72"/>
-      <c r="X249" s="72"/>
+      <c r="W249" s="13"/>
+      <c r="X249" s="13"/>
       <c r="Y249" s="55"/>
       <c r="Z249" s="55"/>
       <c r="AA249" s="55"/>
@@ -14712,8 +14709,8 @@
       <c r="T250" s="13"/>
       <c r="U250" s="13"/>
       <c r="V250" s="13"/>
-      <c r="W250" s="72"/>
-      <c r="X250" s="72"/>
+      <c r="W250" s="13"/>
+      <c r="X250" s="13"/>
       <c r="Y250" s="55"/>
       <c r="Z250" s="55"/>
       <c r="AA250" s="55"/>
@@ -14745,8 +14742,8 @@
       <c r="T251" s="13"/>
       <c r="U251" s="13"/>
       <c r="V251" s="14"/>
-      <c r="W251" s="72"/>
-      <c r="X251" s="72"/>
+      <c r="W251" s="13"/>
+      <c r="X251" s="13"/>
       <c r="Y251" s="55"/>
       <c r="Z251" s="55"/>
       <c r="AA251" s="55"/>
@@ -14778,8 +14775,8 @@
       <c r="T252" s="13"/>
       <c r="U252" s="13"/>
       <c r="V252" s="13"/>
-      <c r="W252" s="72"/>
-      <c r="X252" s="72"/>
+      <c r="W252" s="13"/>
+      <c r="X252" s="13"/>
       <c r="Y252" s="55"/>
       <c r="Z252" s="55"/>
       <c r="AA252" s="55"/>
@@ -14811,8 +14808,8 @@
       <c r="T253" s="13"/>
       <c r="U253" s="13"/>
       <c r="V253" s="13"/>
-      <c r="W253" s="72"/>
-      <c r="X253" s="72"/>
+      <c r="W253" s="13"/>
+      <c r="X253" s="13"/>
       <c r="Y253" s="55"/>
       <c r="Z253" s="55"/>
       <c r="AA253" s="55"/>
@@ -14844,8 +14841,8 @@
       <c r="T254" s="13"/>
       <c r="U254" s="13"/>
       <c r="V254" s="13"/>
-      <c r="W254" s="72"/>
-      <c r="X254" s="72"/>
+      <c r="W254" s="13"/>
+      <c r="X254" s="13"/>
       <c r="Y254" s="55"/>
       <c r="Z254" s="55"/>
       <c r="AA254" s="55"/>
@@ -14877,8 +14874,8 @@
       <c r="T255" s="13"/>
       <c r="U255" s="13"/>
       <c r="V255" s="14"/>
-      <c r="W255" s="72"/>
-      <c r="X255" s="72"/>
+      <c r="W255" s="13"/>
+      <c r="X255" s="13"/>
       <c r="Y255" s="55"/>
       <c r="Z255" s="55"/>
       <c r="AA255" s="55"/>
@@ -14910,8 +14907,8 @@
       <c r="T256" s="13"/>
       <c r="U256" s="13"/>
       <c r="V256" s="13"/>
-      <c r="W256" s="72"/>
-      <c r="X256" s="72"/>
+      <c r="W256" s="13"/>
+      <c r="X256" s="13"/>
       <c r="Y256" s="55"/>
       <c r="Z256" s="55"/>
       <c r="AA256" s="55"/>
@@ -14943,8 +14940,8 @@
       <c r="T257" s="13"/>
       <c r="U257" s="13"/>
       <c r="V257" s="13"/>
-      <c r="W257" s="72"/>
-      <c r="X257" s="72"/>
+      <c r="W257" s="13"/>
+      <c r="X257" s="13"/>
       <c r="Y257" s="55"/>
       <c r="Z257" s="55"/>
       <c r="AA257" s="55"/>
@@ -14976,8 +14973,8 @@
       <c r="T258" s="13"/>
       <c r="U258" s="13"/>
       <c r="V258" s="13"/>
-      <c r="W258" s="72"/>
-      <c r="X258" s="72"/>
+      <c r="W258" s="13"/>
+      <c r="X258" s="13"/>
       <c r="Y258" s="55"/>
       <c r="Z258" s="55"/>
       <c r="AA258" s="55"/>
@@ -15009,8 +15006,8 @@
       <c r="T259" s="13"/>
       <c r="U259" s="13"/>
       <c r="V259" s="13"/>
-      <c r="W259" s="72"/>
-      <c r="X259" s="72"/>
+      <c r="W259" s="13"/>
+      <c r="X259" s="13"/>
       <c r="Y259" s="55"/>
       <c r="Z259" s="55"/>
       <c r="AA259" s="55"/>
@@ -15021,15 +15018,15 @@
     </row>
     <row r="260" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A260" s="54"/>
-      <c r="B260" s="73" t="s">
+      <c r="B260" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="C260" s="74"/>
-      <c r="D260" s="74"/>
-      <c r="E260" s="74"/>
-      <c r="F260" s="74"/>
-      <c r="G260" s="74"/>
-      <c r="H260" s="75"/>
+      <c r="C260" s="73"/>
+      <c r="D260" s="73"/>
+      <c r="E260" s="73"/>
+      <c r="F260" s="73"/>
+      <c r="G260" s="73"/>
+      <c r="H260" s="74"/>
       <c r="I260" s="54"/>
       <c r="J260" s="9"/>
       <c r="K260" s="10"/>
@@ -15044,8 +15041,8 @@
       <c r="T260" s="13"/>
       <c r="U260" s="13"/>
       <c r="V260" s="13"/>
-      <c r="W260" s="72"/>
-      <c r="X260" s="72"/>
+      <c r="W260" s="13"/>
+      <c r="X260" s="13"/>
       <c r="Y260" s="55"/>
       <c r="Z260" s="55"/>
       <c r="AA260" s="55"/>
@@ -15056,13 +15053,13 @@
     </row>
     <row r="261" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A261" s="54"/>
-      <c r="B261" s="76"/>
-      <c r="C261" s="77"/>
-      <c r="D261" s="77"/>
-      <c r="E261" s="77"/>
-      <c r="F261" s="77"/>
-      <c r="G261" s="77"/>
-      <c r="H261" s="78"/>
+      <c r="B261" s="75"/>
+      <c r="C261" s="76"/>
+      <c r="D261" s="76"/>
+      <c r="E261" s="76"/>
+      <c r="F261" s="76"/>
+      <c r="G261" s="76"/>
+      <c r="H261" s="77"/>
       <c r="I261" s="54"/>
       <c r="J261" s="9"/>
       <c r="K261" s="10"/>
@@ -15077,8 +15074,8 @@
       <c r="T261" s="13"/>
       <c r="U261" s="13"/>
       <c r="V261" s="13"/>
-      <c r="W261" s="72"/>
-      <c r="X261" s="72"/>
+      <c r="W261" s="13"/>
+      <c r="X261" s="13"/>
       <c r="Y261" s="55"/>
       <c r="Z261" s="55"/>
       <c r="AA261" s="55"/>
@@ -15089,13 +15086,13 @@
     </row>
     <row r="262" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A262" s="54"/>
-      <c r="B262" s="76"/>
-      <c r="C262" s="77"/>
-      <c r="D262" s="77"/>
-      <c r="E262" s="77"/>
-      <c r="F262" s="77"/>
-      <c r="G262" s="77"/>
-      <c r="H262" s="78"/>
+      <c r="B262" s="75"/>
+      <c r="C262" s="76"/>
+      <c r="D262" s="76"/>
+      <c r="E262" s="76"/>
+      <c r="F262" s="76"/>
+      <c r="G262" s="76"/>
+      <c r="H262" s="77"/>
       <c r="I262" s="54"/>
       <c r="J262" s="9"/>
       <c r="K262" s="10"/>
@@ -15110,8 +15107,8 @@
       <c r="T262" s="13"/>
       <c r="U262" s="13"/>
       <c r="V262" s="13"/>
-      <c r="W262" s="72"/>
-      <c r="X262" s="72"/>
+      <c r="W262" s="13"/>
+      <c r="X262" s="13"/>
       <c r="Y262" s="55"/>
       <c r="Z262" s="55"/>
       <c r="AA262" s="55"/>
@@ -15122,13 +15119,13 @@
     </row>
     <row r="263" spans="1:29" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="54"/>
-      <c r="B263" s="79"/>
-      <c r="C263" s="80"/>
-      <c r="D263" s="80"/>
-      <c r="E263" s="80"/>
-      <c r="F263" s="80"/>
-      <c r="G263" s="80"/>
-      <c r="H263" s="81"/>
+      <c r="B263" s="78"/>
+      <c r="C263" s="79"/>
+      <c r="D263" s="79"/>
+      <c r="E263" s="79"/>
+      <c r="F263" s="79"/>
+      <c r="G263" s="79"/>
+      <c r="H263" s="80"/>
       <c r="I263" s="54"/>
       <c r="J263" s="9"/>
       <c r="K263" s="10"/>
@@ -15143,8 +15140,8 @@
       <c r="T263" s="13"/>
       <c r="U263" s="13"/>
       <c r="V263" s="13"/>
-      <c r="W263" s="72"/>
-      <c r="X263" s="72"/>
+      <c r="W263" s="13"/>
+      <c r="X263" s="13"/>
       <c r="Y263" s="55"/>
       <c r="Z263" s="55"/>
       <c r="AA263" s="55"/>
@@ -15176,8 +15173,8 @@
       <c r="T264" s="13"/>
       <c r="U264" s="13"/>
       <c r="V264" s="13"/>
-      <c r="W264" s="72"/>
-      <c r="X264" s="72"/>
+      <c r="W264" s="13"/>
+      <c r="X264" s="13"/>
       <c r="Y264" s="55"/>
       <c r="Z264" s="55"/>
       <c r="AA264" s="55"/>
@@ -15209,8 +15206,8 @@
       <c r="T265" s="13"/>
       <c r="U265" s="13"/>
       <c r="V265" s="13"/>
-      <c r="W265" s="72"/>
-      <c r="X265" s="72"/>
+      <c r="W265" s="13"/>
+      <c r="X265" s="13"/>
       <c r="Y265" s="55"/>
       <c r="Z265" s="55"/>
       <c r="AA265" s="55"/>
@@ -15242,8 +15239,8 @@
       <c r="T266" s="13"/>
       <c r="U266" s="13"/>
       <c r="V266" s="13"/>
-      <c r="W266" s="72"/>
-      <c r="X266" s="72"/>
+      <c r="W266" s="13"/>
+      <c r="X266" s="13"/>
       <c r="Y266" s="55"/>
       <c r="Z266" s="55"/>
       <c r="AA266" s="55"/>
@@ -15275,8 +15272,8 @@
       <c r="T267" s="13"/>
       <c r="U267" s="13"/>
       <c r="V267" s="13"/>
-      <c r="W267" s="72"/>
-      <c r="X267" s="72"/>
+      <c r="W267" s="13"/>
+      <c r="X267" s="13"/>
       <c r="Y267" s="55"/>
       <c r="Z267" s="55"/>
       <c r="AA267" s="55"/>
@@ -15308,8 +15305,8 @@
       <c r="T268" s="13"/>
       <c r="U268" s="13"/>
       <c r="V268" s="13"/>
-      <c r="W268" s="72"/>
-      <c r="X268" s="72"/>
+      <c r="W268" s="13"/>
+      <c r="X268" s="13"/>
       <c r="Y268" s="55"/>
       <c r="Z268" s="55"/>
       <c r="AA268" s="55"/>
@@ -15341,8 +15338,8 @@
       <c r="T269" s="13"/>
       <c r="U269" s="13"/>
       <c r="V269" s="13"/>
-      <c r="W269" s="72"/>
-      <c r="X269" s="72"/>
+      <c r="W269" s="13"/>
+      <c r="X269" s="13"/>
       <c r="Y269" s="55"/>
       <c r="Z269" s="55"/>
       <c r="AA269" s="55"/>
@@ -15374,8 +15371,8 @@
       <c r="T270" s="13"/>
       <c r="U270" s="13"/>
       <c r="V270" s="13"/>
-      <c r="W270" s="72"/>
-      <c r="X270" s="72"/>
+      <c r="W270" s="13"/>
+      <c r="X270" s="13"/>
       <c r="Y270" s="55"/>
       <c r="Z270" s="55"/>
       <c r="AA270" s="55"/>
@@ -15385,23 +15382,23 @@
       <c r="AC270" s="70"/>
     </row>
     <row r="271" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A271" s="64"/>
-      <c r="B271" s="64"/>
-      <c r="C271" s="64"/>
-      <c r="D271" s="64"/>
-      <c r="E271" s="64"/>
-      <c r="F271" s="64"/>
-      <c r="G271" s="64"/>
+      <c r="A271" s="63"/>
+      <c r="B271" s="63"/>
+      <c r="C271" s="63"/>
+      <c r="D271" s="63"/>
+      <c r="E271" s="63"/>
+      <c r="F271" s="63"/>
+      <c r="G271" s="63"/>
       <c r="H271" s="52"/>
-      <c r="I271" s="64"/>
-      <c r="J271" s="64"/>
-      <c r="K271" s="64"/>
-      <c r="L271" s="64"/>
-      <c r="M271" s="64"/>
-      <c r="N271" s="64"/>
-      <c r="O271" s="64"/>
-      <c r="P271" s="64"/>
-      <c r="Q271" s="64"/>
+      <c r="I271" s="63"/>
+      <c r="J271" s="63"/>
+      <c r="K271" s="63"/>
+      <c r="L271" s="63"/>
+      <c r="M271" s="63"/>
+      <c r="N271" s="63"/>
+      <c r="O271" s="63"/>
+      <c r="P271" s="63"/>
+      <c r="Q271" s="63"/>
       <c r="R271" s="52"/>
       <c r="S271" s="52"/>
       <c r="T271" s="52"/>
@@ -15447,17 +15444,17 @@
     </row>
     <row r="273" spans="1:29" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" s="54"/>
-      <c r="B273" s="82" t="s">
+      <c r="B273" s="81" t="s">
         <v>290</v>
       </c>
-      <c r="C273" s="82"/>
-      <c r="D273" s="82"/>
-      <c r="E273" s="82"/>
-      <c r="F273" s="82"/>
+      <c r="C273" s="81"/>
+      <c r="D273" s="81"/>
+      <c r="E273" s="81"/>
+      <c r="F273" s="81"/>
       <c r="G273" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="H273" s="63">
+      <c r="H273" s="62">
         <f>IFERROR(COUNTIFS(L275:L315, "&lt;&gt;", M275:M315, "", N275:N315, "") / COUNTA(L275:L315), 0)</f>
         <v>0</v>
       </c>
@@ -15506,10 +15503,10 @@
         <v>7</v>
       </c>
       <c r="I274" s="54"/>
-      <c r="J274" s="58" t="s">
+      <c r="J274" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="K274" s="59" t="s">
+      <c r="K274" s="58" t="s">
         <v>21</v>
       </c>
       <c r="L274" s="51" t="s">
@@ -15524,41 +15521,41 @@
       <c r="O274" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="P274" s="60" t="s">
+      <c r="P274" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="Q274" s="60" t="s">
+      <c r="Q274" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="R274" s="61" t="s">
+      <c r="R274" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="S274" s="61" t="s">
+      <c r="S274" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="T274" s="61" t="s">
+      <c r="T274" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="U274" s="62" t="s">
+      <c r="U274" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="V274" s="62" t="s">
+      <c r="V274" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="W274" s="61" t="s">
+      <c r="W274" s="60" t="s">
         <v>329</v>
       </c>
-      <c r="X274" s="61"/>
-      <c r="Y274" s="61" t="s">
+      <c r="X274" s="60"/>
+      <c r="Y274" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="Z274" s="61" t="s">
+      <c r="Z274" s="60" t="s">
         <v>313</v>
       </c>
-      <c r="AA274" s="61" t="s">
+      <c r="AA274" s="60" t="s">
         <v>325</v>
       </c>
-      <c r="AB274" s="61" t="s">
+      <c r="AB274" s="60" t="s">
         <v>27</v>
       </c>
       <c r="AC274" s="71" t="s">
@@ -15592,8 +15589,8 @@
       <c r="T275" s="13"/>
       <c r="U275" s="13"/>
       <c r="V275" s="14"/>
-      <c r="W275" s="72"/>
-      <c r="X275" s="72"/>
+      <c r="W275" s="13"/>
+      <c r="X275" s="13"/>
       <c r="Y275" s="55"/>
       <c r="Z275" s="55"/>
       <c r="AA275" s="55"/>
@@ -15625,8 +15622,8 @@
       <c r="T276" s="13"/>
       <c r="U276" s="13"/>
       <c r="V276" s="14"/>
-      <c r="W276" s="72"/>
-      <c r="X276" s="72"/>
+      <c r="W276" s="13"/>
+      <c r="X276" s="13"/>
       <c r="Y276" s="55"/>
       <c r="Z276" s="55"/>
       <c r="AA276" s="55"/>
@@ -15658,8 +15655,8 @@
       <c r="T277" s="13"/>
       <c r="U277" s="13"/>
       <c r="V277" s="14"/>
-      <c r="W277" s="72"/>
-      <c r="X277" s="72"/>
+      <c r="W277" s="13"/>
+      <c r="X277" s="13"/>
       <c r="Y277" s="55"/>
       <c r="Z277" s="55"/>
       <c r="AA277" s="55"/>
@@ -15691,8 +15688,8 @@
       <c r="T278" s="13"/>
       <c r="U278" s="13"/>
       <c r="V278" s="14"/>
-      <c r="W278" s="72"/>
-      <c r="X278" s="72"/>
+      <c r="W278" s="13"/>
+      <c r="X278" s="13"/>
       <c r="Y278" s="55"/>
       <c r="Z278" s="55"/>
       <c r="AA278" s="55"/>
@@ -15724,8 +15721,8 @@
       <c r="T279" s="13"/>
       <c r="U279" s="13"/>
       <c r="V279" s="14"/>
-      <c r="W279" s="72"/>
-      <c r="X279" s="72"/>
+      <c r="W279" s="13"/>
+      <c r="X279" s="13"/>
       <c r="Y279" s="55"/>
       <c r="Z279" s="55"/>
       <c r="AA279" s="55"/>
@@ -15771,8 +15768,8 @@
       <c r="T280" s="13"/>
       <c r="U280" s="13"/>
       <c r="V280" s="14"/>
-      <c r="W280" s="72"/>
-      <c r="X280" s="72"/>
+      <c r="W280" s="13"/>
+      <c r="X280" s="13"/>
       <c r="Y280" s="55"/>
       <c r="Z280" s="55"/>
       <c r="AA280" s="55"/>
@@ -15804,8 +15801,8 @@
       <c r="T281" s="13"/>
       <c r="U281" s="13"/>
       <c r="V281" s="14"/>
-      <c r="W281" s="72"/>
-      <c r="X281" s="72"/>
+      <c r="W281" s="13"/>
+      <c r="X281" s="13"/>
       <c r="Y281" s="55"/>
       <c r="Z281" s="55"/>
       <c r="AA281" s="55"/>
@@ -15837,8 +15834,8 @@
       <c r="T282" s="13"/>
       <c r="U282" s="13"/>
       <c r="V282" s="14"/>
-      <c r="W282" s="72"/>
-      <c r="X282" s="72"/>
+      <c r="W282" s="13"/>
+      <c r="X282" s="13"/>
       <c r="Y282" s="55"/>
       <c r="Z282" s="55"/>
       <c r="AA282" s="55"/>
@@ -15870,8 +15867,8 @@
       <c r="T283" s="13"/>
       <c r="U283" s="13"/>
       <c r="V283" s="14"/>
-      <c r="W283" s="72"/>
-      <c r="X283" s="72"/>
+      <c r="W283" s="13"/>
+      <c r="X283" s="13"/>
       <c r="Y283" s="55"/>
       <c r="Z283" s="55"/>
       <c r="AA283" s="55"/>
@@ -15903,8 +15900,8 @@
       <c r="T284" s="13"/>
       <c r="U284" s="13"/>
       <c r="V284" s="14"/>
-      <c r="W284" s="72"/>
-      <c r="X284" s="72"/>
+      <c r="W284" s="13"/>
+      <c r="X284" s="13"/>
       <c r="Y284" s="55"/>
       <c r="Z284" s="55"/>
       <c r="AA284" s="55"/>
@@ -15950,8 +15947,8 @@
       <c r="T285" s="13"/>
       <c r="U285" s="13"/>
       <c r="V285" s="14"/>
-      <c r="W285" s="72"/>
-      <c r="X285" s="72"/>
+      <c r="W285" s="13"/>
+      <c r="X285" s="13"/>
       <c r="Y285" s="55"/>
       <c r="Z285" s="55"/>
       <c r="AA285" s="55"/>
@@ -15983,8 +15980,8 @@
       <c r="T286" s="13"/>
       <c r="U286" s="13"/>
       <c r="V286" s="14"/>
-      <c r="W286" s="72"/>
-      <c r="X286" s="72"/>
+      <c r="W286" s="13"/>
+      <c r="X286" s="13"/>
       <c r="Y286" s="55"/>
       <c r="Z286" s="55"/>
       <c r="AA286" s="55"/>
@@ -16016,8 +16013,8 @@
       <c r="T287" s="13"/>
       <c r="U287" s="13"/>
       <c r="V287" s="14"/>
-      <c r="W287" s="72"/>
-      <c r="X287" s="72"/>
+      <c r="W287" s="13"/>
+      <c r="X287" s="13"/>
       <c r="Y287" s="55"/>
       <c r="Z287" s="55"/>
       <c r="AA287" s="55"/>
@@ -16049,8 +16046,8 @@
       <c r="T288" s="13"/>
       <c r="U288" s="13"/>
       <c r="V288" s="14"/>
-      <c r="W288" s="72"/>
-      <c r="X288" s="72"/>
+      <c r="W288" s="13"/>
+      <c r="X288" s="13"/>
       <c r="Y288" s="55"/>
       <c r="Z288" s="55"/>
       <c r="AA288" s="55"/>
@@ -16082,8 +16079,8 @@
       <c r="T289" s="13"/>
       <c r="U289" s="13"/>
       <c r="V289" s="14"/>
-      <c r="W289" s="72"/>
-      <c r="X289" s="72"/>
+      <c r="W289" s="13"/>
+      <c r="X289" s="13"/>
       <c r="Y289" s="55"/>
       <c r="Z289" s="55"/>
       <c r="AA289" s="55"/>
@@ -16129,8 +16126,8 @@
       <c r="T290" s="13"/>
       <c r="U290" s="13"/>
       <c r="V290" s="14"/>
-      <c r="W290" s="72"/>
-      <c r="X290" s="72"/>
+      <c r="W290" s="13"/>
+      <c r="X290" s="13"/>
       <c r="Y290" s="55"/>
       <c r="Z290" s="55"/>
       <c r="AA290" s="55"/>
@@ -16162,8 +16159,8 @@
       <c r="T291" s="13"/>
       <c r="U291" s="13"/>
       <c r="V291" s="13"/>
-      <c r="W291" s="72"/>
-      <c r="X291" s="72"/>
+      <c r="W291" s="13"/>
+      <c r="X291" s="13"/>
       <c r="Y291" s="55"/>
       <c r="Z291" s="55"/>
       <c r="AA291" s="55"/>
@@ -16195,8 +16192,8 @@
       <c r="T292" s="13"/>
       <c r="U292" s="13"/>
       <c r="V292" s="13"/>
-      <c r="W292" s="72"/>
-      <c r="X292" s="72"/>
+      <c r="W292" s="13"/>
+      <c r="X292" s="13"/>
       <c r="Y292" s="55"/>
       <c r="Z292" s="55"/>
       <c r="AA292" s="55"/>
@@ -16228,8 +16225,8 @@
       <c r="T293" s="13"/>
       <c r="U293" s="13"/>
       <c r="V293" s="13"/>
-      <c r="W293" s="72"/>
-      <c r="X293" s="72"/>
+      <c r="W293" s="13"/>
+      <c r="X293" s="13"/>
       <c r="Y293" s="55"/>
       <c r="Z293" s="55"/>
       <c r="AA293" s="55"/>
@@ -16261,8 +16258,8 @@
       <c r="T294" s="13"/>
       <c r="U294" s="13"/>
       <c r="V294" s="13"/>
-      <c r="W294" s="72"/>
-      <c r="X294" s="72"/>
+      <c r="W294" s="13"/>
+      <c r="X294" s="13"/>
       <c r="Y294" s="55"/>
       <c r="Z294" s="55"/>
       <c r="AA294" s="55"/>
@@ -16308,8 +16305,8 @@
       <c r="T295" s="13"/>
       <c r="U295" s="13"/>
       <c r="V295" s="13"/>
-      <c r="W295" s="72"/>
-      <c r="X295" s="72"/>
+      <c r="W295" s="13"/>
+      <c r="X295" s="13"/>
       <c r="Y295" s="55"/>
       <c r="Z295" s="55"/>
       <c r="AA295" s="55"/>
@@ -16341,8 +16338,8 @@
       <c r="T296" s="13"/>
       <c r="U296" s="13"/>
       <c r="V296" s="14"/>
-      <c r="W296" s="72"/>
-      <c r="X296" s="72"/>
+      <c r="W296" s="13"/>
+      <c r="X296" s="13"/>
       <c r="Y296" s="55"/>
       <c r="Z296" s="55"/>
       <c r="AA296" s="55"/>
@@ -16374,8 +16371,8 @@
       <c r="T297" s="13"/>
       <c r="U297" s="13"/>
       <c r="V297" s="13"/>
-      <c r="W297" s="72"/>
-      <c r="X297" s="72"/>
+      <c r="W297" s="13"/>
+      <c r="X297" s="13"/>
       <c r="Y297" s="55"/>
       <c r="Z297" s="55"/>
       <c r="AA297" s="55"/>
@@ -16407,8 +16404,8 @@
       <c r="T298" s="13"/>
       <c r="U298" s="13"/>
       <c r="V298" s="13"/>
-      <c r="W298" s="72"/>
-      <c r="X298" s="72"/>
+      <c r="W298" s="13"/>
+      <c r="X298" s="13"/>
       <c r="Y298" s="55"/>
       <c r="Z298" s="55"/>
       <c r="AA298" s="55"/>
@@ -16440,8 +16437,8 @@
       <c r="T299" s="13"/>
       <c r="U299" s="13"/>
       <c r="V299" s="13"/>
-      <c r="W299" s="72"/>
-      <c r="X299" s="72"/>
+      <c r="W299" s="13"/>
+      <c r="X299" s="13"/>
       <c r="Y299" s="55"/>
       <c r="Z299" s="55"/>
       <c r="AA299" s="55"/>
@@ -16475,8 +16472,8 @@
       <c r="T300" s="13"/>
       <c r="U300" s="13"/>
       <c r="V300" s="14"/>
-      <c r="W300" s="72"/>
-      <c r="X300" s="72"/>
+      <c r="W300" s="13"/>
+      <c r="X300" s="13"/>
       <c r="Y300" s="55"/>
       <c r="Z300" s="55"/>
       <c r="AA300" s="55"/>
@@ -16508,8 +16505,8 @@
       <c r="T301" s="13"/>
       <c r="U301" s="13"/>
       <c r="V301" s="13"/>
-      <c r="W301" s="72"/>
-      <c r="X301" s="72"/>
+      <c r="W301" s="13"/>
+      <c r="X301" s="13"/>
       <c r="Y301" s="55"/>
       <c r="Z301" s="55"/>
       <c r="AA301" s="55"/>
@@ -16541,8 +16538,8 @@
       <c r="T302" s="13"/>
       <c r="U302" s="13"/>
       <c r="V302" s="13"/>
-      <c r="W302" s="72"/>
-      <c r="X302" s="72"/>
+      <c r="W302" s="13"/>
+      <c r="X302" s="13"/>
       <c r="Y302" s="55"/>
       <c r="Z302" s="55"/>
       <c r="AA302" s="55"/>
@@ -16574,8 +16571,8 @@
       <c r="T303" s="13"/>
       <c r="U303" s="13"/>
       <c r="V303" s="13"/>
-      <c r="W303" s="72"/>
-      <c r="X303" s="72"/>
+      <c r="W303" s="13"/>
+      <c r="X303" s="13"/>
       <c r="Y303" s="55"/>
       <c r="Z303" s="55"/>
       <c r="AA303" s="55"/>
@@ -16607,8 +16604,8 @@
       <c r="T304" s="13"/>
       <c r="U304" s="13"/>
       <c r="V304" s="13"/>
-      <c r="W304" s="72"/>
-      <c r="X304" s="72"/>
+      <c r="W304" s="13"/>
+      <c r="X304" s="13"/>
       <c r="Y304" s="55"/>
       <c r="Z304" s="55"/>
       <c r="AA304" s="55"/>
@@ -16619,15 +16616,15 @@
     </row>
     <row r="305" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A305" s="54"/>
-      <c r="B305" s="73" t="s">
+      <c r="B305" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="C305" s="74"/>
-      <c r="D305" s="74"/>
-      <c r="E305" s="74"/>
-      <c r="F305" s="74"/>
-      <c r="G305" s="74"/>
-      <c r="H305" s="75"/>
+      <c r="C305" s="73"/>
+      <c r="D305" s="73"/>
+      <c r="E305" s="73"/>
+      <c r="F305" s="73"/>
+      <c r="G305" s="73"/>
+      <c r="H305" s="74"/>
       <c r="I305" s="54"/>
       <c r="J305" s="9"/>
       <c r="K305" s="10"/>
@@ -16642,8 +16639,8 @@
       <c r="T305" s="13"/>
       <c r="U305" s="13"/>
       <c r="V305" s="13"/>
-      <c r="W305" s="72"/>
-      <c r="X305" s="72"/>
+      <c r="W305" s="13"/>
+      <c r="X305" s="13"/>
       <c r="Y305" s="55"/>
       <c r="Z305" s="55"/>
       <c r="AA305" s="55"/>
@@ -16654,13 +16651,13 @@
     </row>
     <row r="306" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A306" s="54"/>
-      <c r="B306" s="76"/>
-      <c r="C306" s="77"/>
-      <c r="D306" s="77"/>
-      <c r="E306" s="77"/>
-      <c r="F306" s="77"/>
-      <c r="G306" s="77"/>
-      <c r="H306" s="78"/>
+      <c r="B306" s="75"/>
+      <c r="C306" s="76"/>
+      <c r="D306" s="76"/>
+      <c r="E306" s="76"/>
+      <c r="F306" s="76"/>
+      <c r="G306" s="76"/>
+      <c r="H306" s="77"/>
       <c r="I306" s="54"/>
       <c r="J306" s="9"/>
       <c r="K306" s="10"/>
@@ -16675,8 +16672,8 @@
       <c r="T306" s="13"/>
       <c r="U306" s="13"/>
       <c r="V306" s="13"/>
-      <c r="W306" s="72"/>
-      <c r="X306" s="72"/>
+      <c r="W306" s="13"/>
+      <c r="X306" s="13"/>
       <c r="Y306" s="55"/>
       <c r="Z306" s="55"/>
       <c r="AA306" s="55"/>
@@ -16687,13 +16684,13 @@
     </row>
     <row r="307" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A307" s="54"/>
-      <c r="B307" s="76"/>
-      <c r="C307" s="77"/>
-      <c r="D307" s="77"/>
-      <c r="E307" s="77"/>
-      <c r="F307" s="77"/>
-      <c r="G307" s="77"/>
-      <c r="H307" s="78"/>
+      <c r="B307" s="75"/>
+      <c r="C307" s="76"/>
+      <c r="D307" s="76"/>
+      <c r="E307" s="76"/>
+      <c r="F307" s="76"/>
+      <c r="G307" s="76"/>
+      <c r="H307" s="77"/>
       <c r="I307" s="54"/>
       <c r="J307" s="9"/>
       <c r="K307" s="10"/>
@@ -16708,8 +16705,8 @@
       <c r="T307" s="13"/>
       <c r="U307" s="13"/>
       <c r="V307" s="13"/>
-      <c r="W307" s="72"/>
-      <c r="X307" s="72"/>
+      <c r="W307" s="13"/>
+      <c r="X307" s="13"/>
       <c r="Y307" s="55"/>
       <c r="Z307" s="55"/>
       <c r="AA307" s="55"/>
@@ -16720,13 +16717,13 @@
     </row>
     <row r="308" spans="1:29" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A308" s="54"/>
-      <c r="B308" s="79"/>
-      <c r="C308" s="80"/>
-      <c r="D308" s="80"/>
-      <c r="E308" s="80"/>
-      <c r="F308" s="80"/>
-      <c r="G308" s="80"/>
-      <c r="H308" s="81"/>
+      <c r="B308" s="78"/>
+      <c r="C308" s="79"/>
+      <c r="D308" s="79"/>
+      <c r="E308" s="79"/>
+      <c r="F308" s="79"/>
+      <c r="G308" s="79"/>
+      <c r="H308" s="80"/>
       <c r="I308" s="54"/>
       <c r="J308" s="9"/>
       <c r="K308" s="10"/>
@@ -16741,8 +16738,8 @@
       <c r="T308" s="13"/>
       <c r="U308" s="13"/>
       <c r="V308" s="13"/>
-      <c r="W308" s="72"/>
-      <c r="X308" s="72"/>
+      <c r="W308" s="13"/>
+      <c r="X308" s="13"/>
       <c r="Y308" s="55"/>
       <c r="Z308" s="55"/>
       <c r="AA308" s="55"/>
@@ -16774,8 +16771,8 @@
       <c r="T309" s="13"/>
       <c r="U309" s="13"/>
       <c r="V309" s="13"/>
-      <c r="W309" s="72"/>
-      <c r="X309" s="72"/>
+      <c r="W309" s="13"/>
+      <c r="X309" s="13"/>
       <c r="Y309" s="55"/>
       <c r="Z309" s="55"/>
       <c r="AA309" s="55"/>
@@ -16807,8 +16804,8 @@
       <c r="T310" s="13"/>
       <c r="U310" s="13"/>
       <c r="V310" s="13"/>
-      <c r="W310" s="72"/>
-      <c r="X310" s="72"/>
+      <c r="W310" s="13"/>
+      <c r="X310" s="13"/>
       <c r="Y310" s="55"/>
       <c r="Z310" s="55"/>
       <c r="AA310" s="55"/>
@@ -16840,8 +16837,8 @@
       <c r="T311" s="13"/>
       <c r="U311" s="13"/>
       <c r="V311" s="13"/>
-      <c r="W311" s="72"/>
-      <c r="X311" s="72"/>
+      <c r="W311" s="13"/>
+      <c r="X311" s="13"/>
       <c r="Y311" s="55"/>
       <c r="Z311" s="55"/>
       <c r="AA311" s="55"/>
@@ -16873,8 +16870,8 @@
       <c r="T312" s="13"/>
       <c r="U312" s="13"/>
       <c r="V312" s="13"/>
-      <c r="W312" s="72"/>
-      <c r="X312" s="72"/>
+      <c r="W312" s="13"/>
+      <c r="X312" s="13"/>
       <c r="Y312" s="55"/>
       <c r="Z312" s="55"/>
       <c r="AA312" s="55"/>
@@ -16906,8 +16903,8 @@
       <c r="T313" s="13"/>
       <c r="U313" s="13"/>
       <c r="V313" s="13"/>
-      <c r="W313" s="72"/>
-      <c r="X313" s="72"/>
+      <c r="W313" s="13"/>
+      <c r="X313" s="13"/>
       <c r="Y313" s="55"/>
       <c r="Z313" s="55"/>
       <c r="AA313" s="55"/>
@@ -16939,8 +16936,8 @@
       <c r="T314" s="13"/>
       <c r="U314" s="13"/>
       <c r="V314" s="13"/>
-      <c r="W314" s="72"/>
-      <c r="X314" s="72"/>
+      <c r="W314" s="13"/>
+      <c r="X314" s="13"/>
       <c r="Y314" s="55"/>
       <c r="Z314" s="55"/>
       <c r="AA314" s="55"/>
@@ -16972,8 +16969,8 @@
       <c r="T315" s="13"/>
       <c r="U315" s="13"/>
       <c r="V315" s="13"/>
-      <c r="W315" s="72"/>
-      <c r="X315" s="72"/>
+      <c r="W315" s="13"/>
+      <c r="X315" s="13"/>
       <c r="Y315" s="55"/>
       <c r="Z315" s="55"/>
       <c r="AA315" s="55"/>
@@ -16983,23 +16980,23 @@
       <c r="AC315" s="70"/>
     </row>
     <row r="316" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A316" s="64"/>
-      <c r="B316" s="64"/>
-      <c r="C316" s="64"/>
-      <c r="D316" s="64"/>
-      <c r="E316" s="64"/>
-      <c r="F316" s="64"/>
-      <c r="G316" s="64"/>
+      <c r="A316" s="63"/>
+      <c r="B316" s="63"/>
+      <c r="C316" s="63"/>
+      <c r="D316" s="63"/>
+      <c r="E316" s="63"/>
+      <c r="F316" s="63"/>
+      <c r="G316" s="63"/>
       <c r="H316" s="52"/>
-      <c r="I316" s="64"/>
-      <c r="J316" s="64"/>
-      <c r="K316" s="64"/>
-      <c r="L316" s="64"/>
-      <c r="M316" s="64"/>
-      <c r="N316" s="64"/>
-      <c r="O316" s="64"/>
-      <c r="P316" s="64"/>
-      <c r="Q316" s="64"/>
+      <c r="I316" s="63"/>
+      <c r="J316" s="63"/>
+      <c r="K316" s="63"/>
+      <c r="L316" s="63"/>
+      <c r="M316" s="63"/>
+      <c r="N316" s="63"/>
+      <c r="O316" s="63"/>
+      <c r="P316" s="63"/>
+      <c r="Q316" s="63"/>
       <c r="R316" s="52"/>
       <c r="S316" s="52"/>
       <c r="T316" s="52"/>
@@ -17045,17 +17042,17 @@
     </row>
     <row r="318" spans="1:29" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A318" s="54"/>
-      <c r="B318" s="82" t="s">
+      <c r="B318" s="81" t="s">
         <v>291</v>
       </c>
-      <c r="C318" s="82"/>
-      <c r="D318" s="82"/>
-      <c r="E318" s="82"/>
-      <c r="F318" s="82"/>
+      <c r="C318" s="81"/>
+      <c r="D318" s="81"/>
+      <c r="E318" s="81"/>
+      <c r="F318" s="81"/>
       <c r="G318" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="H318" s="63">
+      <c r="H318" s="62">
         <f>IFERROR(COUNTIFS(L320:L360, "&lt;&gt;", M320:M360, "", N320:N360, "") / COUNTA(L320:L360), 0)</f>
         <v>0</v>
       </c>
@@ -17104,10 +17101,10 @@
         <v>7</v>
       </c>
       <c r="I319" s="54"/>
-      <c r="J319" s="58" t="s">
+      <c r="J319" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="K319" s="59" t="s">
+      <c r="K319" s="58" t="s">
         <v>21</v>
       </c>
       <c r="L319" s="51" t="s">
@@ -17122,41 +17119,41 @@
       <c r="O319" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="P319" s="60" t="s">
+      <c r="P319" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="Q319" s="60" t="s">
+      <c r="Q319" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="R319" s="61" t="s">
+      <c r="R319" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="S319" s="61" t="s">
+      <c r="S319" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="T319" s="61" t="s">
+      <c r="T319" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="U319" s="62" t="s">
+      <c r="U319" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="V319" s="62" t="s">
+      <c r="V319" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="W319" s="61" t="s">
+      <c r="W319" s="60" t="s">
         <v>329</v>
       </c>
-      <c r="X319" s="61"/>
-      <c r="Y319" s="61" t="s">
+      <c r="X319" s="60"/>
+      <c r="Y319" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="Z319" s="61" t="s">
+      <c r="Z319" s="60" t="s">
         <v>313</v>
       </c>
-      <c r="AA319" s="61" t="s">
+      <c r="AA319" s="60" t="s">
         <v>325</v>
       </c>
-      <c r="AB319" s="61" t="s">
+      <c r="AB319" s="60" t="s">
         <v>27</v>
       </c>
       <c r="AC319" s="71" t="s">
@@ -17198,8 +17195,8 @@
       <c r="T320" s="13"/>
       <c r="U320" s="13"/>
       <c r="V320" s="14"/>
-      <c r="W320" s="72"/>
-      <c r="X320" s="72"/>
+      <c r="W320" s="13"/>
+      <c r="X320" s="13"/>
       <c r="Y320" s="55"/>
       <c r="Z320" s="55"/>
       <c r="AA320" s="55"/>
@@ -17231,8 +17228,8 @@
       <c r="T321" s="13"/>
       <c r="U321" s="13"/>
       <c r="V321" s="14"/>
-      <c r="W321" s="72"/>
-      <c r="X321" s="72"/>
+      <c r="W321" s="13"/>
+      <c r="X321" s="13"/>
       <c r="Y321" s="55"/>
       <c r="Z321" s="55"/>
       <c r="AA321" s="55"/>
@@ -17264,8 +17261,8 @@
       <c r="T322" s="13"/>
       <c r="U322" s="13"/>
       <c r="V322" s="14"/>
-      <c r="W322" s="72"/>
-      <c r="X322" s="72"/>
+      <c r="W322" s="13"/>
+      <c r="X322" s="13"/>
       <c r="Y322" s="55"/>
       <c r="Z322" s="55"/>
       <c r="AA322" s="55"/>
@@ -17297,8 +17294,8 @@
       <c r="T323" s="13"/>
       <c r="U323" s="13"/>
       <c r="V323" s="14"/>
-      <c r="W323" s="72"/>
-      <c r="X323" s="72"/>
+      <c r="W323" s="13"/>
+      <c r="X323" s="13"/>
       <c r="Y323" s="55"/>
       <c r="Z323" s="55"/>
       <c r="AA323" s="55"/>
@@ -17330,8 +17327,8 @@
       <c r="T324" s="13"/>
       <c r="U324" s="13"/>
       <c r="V324" s="14"/>
-      <c r="W324" s="72"/>
-      <c r="X324" s="72"/>
+      <c r="W324" s="13"/>
+      <c r="X324" s="13"/>
       <c r="Y324" s="55"/>
       <c r="Z324" s="55"/>
       <c r="AA324" s="55"/>
@@ -17377,8 +17374,8 @@
       <c r="T325" s="13"/>
       <c r="U325" s="13"/>
       <c r="V325" s="14"/>
-      <c r="W325" s="72"/>
-      <c r="X325" s="72"/>
+      <c r="W325" s="13"/>
+      <c r="X325" s="13"/>
       <c r="Y325" s="55"/>
       <c r="Z325" s="55"/>
       <c r="AA325" s="55"/>
@@ -17410,8 +17407,8 @@
       <c r="T326" s="13"/>
       <c r="U326" s="13"/>
       <c r="V326" s="14"/>
-      <c r="W326" s="72"/>
-      <c r="X326" s="72"/>
+      <c r="W326" s="13"/>
+      <c r="X326" s="13"/>
       <c r="Y326" s="55"/>
       <c r="Z326" s="55"/>
       <c r="AA326" s="55"/>
@@ -17443,8 +17440,8 @@
       <c r="T327" s="13"/>
       <c r="U327" s="13"/>
       <c r="V327" s="14"/>
-      <c r="W327" s="72"/>
-      <c r="X327" s="72"/>
+      <c r="W327" s="13"/>
+      <c r="X327" s="13"/>
       <c r="Y327" s="55"/>
       <c r="Z327" s="55"/>
       <c r="AA327" s="55"/>
@@ -17476,8 +17473,8 @@
       <c r="T328" s="13"/>
       <c r="U328" s="13"/>
       <c r="V328" s="14"/>
-      <c r="W328" s="72"/>
-      <c r="X328" s="72"/>
+      <c r="W328" s="13"/>
+      <c r="X328" s="13"/>
       <c r="Y328" s="55"/>
       <c r="Z328" s="55"/>
       <c r="AA328" s="55"/>
@@ -17509,8 +17506,8 @@
       <c r="T329" s="13"/>
       <c r="U329" s="13"/>
       <c r="V329" s="14"/>
-      <c r="W329" s="72"/>
-      <c r="X329" s="72"/>
+      <c r="W329" s="13"/>
+      <c r="X329" s="13"/>
       <c r="Y329" s="55"/>
       <c r="Z329" s="55"/>
       <c r="AA329" s="55"/>
@@ -17556,8 +17553,8 @@
       <c r="T330" s="13"/>
       <c r="U330" s="13"/>
       <c r="V330" s="14"/>
-      <c r="W330" s="72"/>
-      <c r="X330" s="72"/>
+      <c r="W330" s="13"/>
+      <c r="X330" s="13"/>
       <c r="Y330" s="55"/>
       <c r="Z330" s="55"/>
       <c r="AA330" s="55"/>
@@ -17589,8 +17586,8 @@
       <c r="T331" s="13"/>
       <c r="U331" s="13"/>
       <c r="V331" s="14"/>
-      <c r="W331" s="72"/>
-      <c r="X331" s="72"/>
+      <c r="W331" s="13"/>
+      <c r="X331" s="13"/>
       <c r="Y331" s="55"/>
       <c r="Z331" s="55"/>
       <c r="AA331" s="55"/>
@@ -17622,8 +17619,8 @@
       <c r="T332" s="13"/>
       <c r="U332" s="13"/>
       <c r="V332" s="14"/>
-      <c r="W332" s="72"/>
-      <c r="X332" s="72"/>
+      <c r="W332" s="13"/>
+      <c r="X332" s="13"/>
       <c r="Y332" s="55"/>
       <c r="Z332" s="55"/>
       <c r="AA332" s="55"/>
@@ -17655,8 +17652,8 @@
       <c r="T333" s="13"/>
       <c r="U333" s="13"/>
       <c r="V333" s="14"/>
-      <c r="W333" s="72"/>
-      <c r="X333" s="72"/>
+      <c r="W333" s="13"/>
+      <c r="X333" s="13"/>
       <c r="Y333" s="55"/>
       <c r="Z333" s="55"/>
       <c r="AA333" s="55"/>
@@ -17688,8 +17685,8 @@
       <c r="T334" s="13"/>
       <c r="U334" s="13"/>
       <c r="V334" s="14"/>
-      <c r="W334" s="72"/>
-      <c r="X334" s="72"/>
+      <c r="W334" s="13"/>
+      <c r="X334" s="13"/>
       <c r="Y334" s="55"/>
       <c r="Z334" s="55"/>
       <c r="AA334" s="55"/>
@@ -17735,8 +17732,8 @@
       <c r="T335" s="13"/>
       <c r="U335" s="13"/>
       <c r="V335" s="14"/>
-      <c r="W335" s="72"/>
-      <c r="X335" s="72"/>
+      <c r="W335" s="13"/>
+      <c r="X335" s="13"/>
       <c r="Y335" s="55"/>
       <c r="Z335" s="55"/>
       <c r="AA335" s="55"/>
@@ -17768,8 +17765,8 @@
       <c r="T336" s="13"/>
       <c r="U336" s="13"/>
       <c r="V336" s="13"/>
-      <c r="W336" s="72"/>
-      <c r="X336" s="72"/>
+      <c r="W336" s="13"/>
+      <c r="X336" s="13"/>
       <c r="Y336" s="55"/>
       <c r="Z336" s="55"/>
       <c r="AA336" s="55"/>
@@ -17801,8 +17798,8 @@
       <c r="T337" s="13"/>
       <c r="U337" s="13"/>
       <c r="V337" s="13"/>
-      <c r="W337" s="72"/>
-      <c r="X337" s="72"/>
+      <c r="W337" s="13"/>
+      <c r="X337" s="13"/>
       <c r="Y337" s="55"/>
       <c r="Z337" s="55"/>
       <c r="AA337" s="55"/>
@@ -17834,8 +17831,8 @@
       <c r="T338" s="13"/>
       <c r="U338" s="13"/>
       <c r="V338" s="13"/>
-      <c r="W338" s="72"/>
-      <c r="X338" s="72"/>
+      <c r="W338" s="13"/>
+      <c r="X338" s="13"/>
       <c r="Y338" s="55"/>
       <c r="Z338" s="55"/>
       <c r="AA338" s="55"/>
@@ -17867,8 +17864,8 @@
       <c r="T339" s="13"/>
       <c r="U339" s="13"/>
       <c r="V339" s="13"/>
-      <c r="W339" s="72"/>
-      <c r="X339" s="72"/>
+      <c r="W339" s="13"/>
+      <c r="X339" s="13"/>
       <c r="Y339" s="55"/>
       <c r="Z339" s="55"/>
       <c r="AA339" s="55"/>
@@ -17906,8 +17903,8 @@
       <c r="T340" s="13"/>
       <c r="U340" s="13"/>
       <c r="V340" s="13"/>
-      <c r="W340" s="72"/>
-      <c r="X340" s="72"/>
+      <c r="W340" s="13"/>
+      <c r="X340" s="13"/>
       <c r="Y340" s="55"/>
       <c r="Z340" s="55"/>
       <c r="AA340" s="55"/>
@@ -17939,8 +17936,8 @@
       <c r="T341" s="13"/>
       <c r="U341" s="13"/>
       <c r="V341" s="14"/>
-      <c r="W341" s="72"/>
-      <c r="X341" s="72"/>
+      <c r="W341" s="13"/>
+      <c r="X341" s="13"/>
       <c r="Y341" s="55"/>
       <c r="Z341" s="55"/>
       <c r="AA341" s="55"/>
@@ -17972,8 +17969,8 @@
       <c r="T342" s="13"/>
       <c r="U342" s="13"/>
       <c r="V342" s="13"/>
-      <c r="W342" s="72"/>
-      <c r="X342" s="72"/>
+      <c r="W342" s="13"/>
+      <c r="X342" s="13"/>
       <c r="Y342" s="55"/>
       <c r="Z342" s="55"/>
       <c r="AA342" s="55"/>
@@ -18005,8 +18002,8 @@
       <c r="T343" s="13"/>
       <c r="U343" s="13"/>
       <c r="V343" s="13"/>
-      <c r="W343" s="72"/>
-      <c r="X343" s="72"/>
+      <c r="W343" s="13"/>
+      <c r="X343" s="13"/>
       <c r="Y343" s="55"/>
       <c r="Z343" s="55"/>
       <c r="AA343" s="55"/>
@@ -18038,8 +18035,8 @@
       <c r="T344" s="13"/>
       <c r="U344" s="13"/>
       <c r="V344" s="13"/>
-      <c r="W344" s="72"/>
-      <c r="X344" s="72"/>
+      <c r="W344" s="13"/>
+      <c r="X344" s="13"/>
       <c r="Y344" s="55"/>
       <c r="Z344" s="55"/>
       <c r="AA344" s="55"/>
@@ -18071,8 +18068,8 @@
       <c r="T345" s="13"/>
       <c r="U345" s="13"/>
       <c r="V345" s="14"/>
-      <c r="W345" s="72"/>
-      <c r="X345" s="72"/>
+      <c r="W345" s="13"/>
+      <c r="X345" s="13"/>
       <c r="Y345" s="55"/>
       <c r="Z345" s="55"/>
       <c r="AA345" s="55"/>
@@ -18104,8 +18101,8 @@
       <c r="T346" s="13"/>
       <c r="U346" s="13"/>
       <c r="V346" s="13"/>
-      <c r="W346" s="72"/>
-      <c r="X346" s="72"/>
+      <c r="W346" s="13"/>
+      <c r="X346" s="13"/>
       <c r="Y346" s="55"/>
       <c r="Z346" s="55"/>
       <c r="AA346" s="55"/>
@@ -18137,8 +18134,8 @@
       <c r="T347" s="13"/>
       <c r="U347" s="13"/>
       <c r="V347" s="13"/>
-      <c r="W347" s="72"/>
-      <c r="X347" s="72"/>
+      <c r="W347" s="13"/>
+      <c r="X347" s="13"/>
       <c r="Y347" s="55"/>
       <c r="Z347" s="55"/>
       <c r="AA347" s="55"/>
@@ -18170,8 +18167,8 @@
       <c r="T348" s="13"/>
       <c r="U348" s="13"/>
       <c r="V348" s="13"/>
-      <c r="W348" s="72"/>
-      <c r="X348" s="72"/>
+      <c r="W348" s="13"/>
+      <c r="X348" s="13"/>
       <c r="Y348" s="55"/>
       <c r="Z348" s="55"/>
       <c r="AA348" s="55"/>
@@ -18203,8 +18200,8 @@
       <c r="T349" s="13"/>
       <c r="U349" s="13"/>
       <c r="V349" s="13"/>
-      <c r="W349" s="72"/>
-      <c r="X349" s="72"/>
+      <c r="W349" s="13"/>
+      <c r="X349" s="13"/>
       <c r="Y349" s="55"/>
       <c r="Z349" s="55"/>
       <c r="AA349" s="55"/>
@@ -18215,15 +18212,15 @@
     </row>
     <row r="350" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A350" s="54"/>
-      <c r="B350" s="73" t="s">
+      <c r="B350" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="C350" s="74"/>
-      <c r="D350" s="74"/>
-      <c r="E350" s="74"/>
-      <c r="F350" s="74"/>
-      <c r="G350" s="74"/>
-      <c r="H350" s="75"/>
+      <c r="C350" s="73"/>
+      <c r="D350" s="73"/>
+      <c r="E350" s="73"/>
+      <c r="F350" s="73"/>
+      <c r="G350" s="73"/>
+      <c r="H350" s="74"/>
       <c r="I350" s="54"/>
       <c r="J350" s="9"/>
       <c r="K350" s="10"/>
@@ -18238,8 +18235,8 @@
       <c r="T350" s="13"/>
       <c r="U350" s="13"/>
       <c r="V350" s="13"/>
-      <c r="W350" s="72"/>
-      <c r="X350" s="72"/>
+      <c r="W350" s="13"/>
+      <c r="X350" s="13"/>
       <c r="Y350" s="55"/>
       <c r="Z350" s="55"/>
       <c r="AA350" s="55"/>
@@ -18250,13 +18247,13 @@
     </row>
     <row r="351" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A351" s="54"/>
-      <c r="B351" s="76"/>
-      <c r="C351" s="77"/>
-      <c r="D351" s="77"/>
-      <c r="E351" s="77"/>
-      <c r="F351" s="77"/>
-      <c r="G351" s="77"/>
-      <c r="H351" s="78"/>
+      <c r="B351" s="75"/>
+      <c r="C351" s="76"/>
+      <c r="D351" s="76"/>
+      <c r="E351" s="76"/>
+      <c r="F351" s="76"/>
+      <c r="G351" s="76"/>
+      <c r="H351" s="77"/>
       <c r="I351" s="54"/>
       <c r="J351" s="9"/>
       <c r="K351" s="10"/>
@@ -18271,8 +18268,8 @@
       <c r="T351" s="13"/>
       <c r="U351" s="13"/>
       <c r="V351" s="13"/>
-      <c r="W351" s="72"/>
-      <c r="X351" s="72"/>
+      <c r="W351" s="13"/>
+      <c r="X351" s="13"/>
       <c r="Y351" s="55"/>
       <c r="Z351" s="55"/>
       <c r="AA351" s="55"/>
@@ -18283,13 +18280,13 @@
     </row>
     <row r="352" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A352" s="54"/>
-      <c r="B352" s="76"/>
-      <c r="C352" s="77"/>
-      <c r="D352" s="77"/>
-      <c r="E352" s="77"/>
-      <c r="F352" s="77"/>
-      <c r="G352" s="77"/>
-      <c r="H352" s="78"/>
+      <c r="B352" s="75"/>
+      <c r="C352" s="76"/>
+      <c r="D352" s="76"/>
+      <c r="E352" s="76"/>
+      <c r="F352" s="76"/>
+      <c r="G352" s="76"/>
+      <c r="H352" s="77"/>
       <c r="I352" s="54"/>
       <c r="J352" s="9"/>
       <c r="K352" s="10"/>
@@ -18304,8 +18301,8 @@
       <c r="T352" s="13"/>
       <c r="U352" s="13"/>
       <c r="V352" s="13"/>
-      <c r="W352" s="72"/>
-      <c r="X352" s="72"/>
+      <c r="W352" s="13"/>
+      <c r="X352" s="13"/>
       <c r="Y352" s="55"/>
       <c r="Z352" s="55"/>
       <c r="AA352" s="55"/>
@@ -18316,13 +18313,13 @@
     </row>
     <row r="353" spans="1:29" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A353" s="54"/>
-      <c r="B353" s="79"/>
-      <c r="C353" s="80"/>
-      <c r="D353" s="80"/>
-      <c r="E353" s="80"/>
-      <c r="F353" s="80"/>
-      <c r="G353" s="80"/>
-      <c r="H353" s="81"/>
+      <c r="B353" s="78"/>
+      <c r="C353" s="79"/>
+      <c r="D353" s="79"/>
+      <c r="E353" s="79"/>
+      <c r="F353" s="79"/>
+      <c r="G353" s="79"/>
+      <c r="H353" s="80"/>
       <c r="I353" s="54"/>
       <c r="J353" s="9"/>
       <c r="K353" s="10"/>
@@ -18337,8 +18334,8 @@
       <c r="T353" s="13"/>
       <c r="U353" s="13"/>
       <c r="V353" s="13"/>
-      <c r="W353" s="72"/>
-      <c r="X353" s="72"/>
+      <c r="W353" s="13"/>
+      <c r="X353" s="13"/>
       <c r="Y353" s="55"/>
       <c r="Z353" s="55"/>
       <c r="AA353" s="55"/>
@@ -18370,8 +18367,8 @@
       <c r="T354" s="13"/>
       <c r="U354" s="13"/>
       <c r="V354" s="13"/>
-      <c r="W354" s="72"/>
-      <c r="X354" s="72"/>
+      <c r="W354" s="13"/>
+      <c r="X354" s="13"/>
       <c r="Y354" s="55"/>
       <c r="Z354" s="55"/>
       <c r="AA354" s="55"/>
@@ -18403,8 +18400,8 @@
       <c r="T355" s="13"/>
       <c r="U355" s="13"/>
       <c r="V355" s="13"/>
-      <c r="W355" s="72"/>
-      <c r="X355" s="72"/>
+      <c r="W355" s="13"/>
+      <c r="X355" s="13"/>
       <c r="Y355" s="55"/>
       <c r="Z355" s="55"/>
       <c r="AA355" s="55"/>
@@ -18436,8 +18433,8 @@
       <c r="T356" s="13"/>
       <c r="U356" s="13"/>
       <c r="V356" s="13"/>
-      <c r="W356" s="72"/>
-      <c r="X356" s="72"/>
+      <c r="W356" s="13"/>
+      <c r="X356" s="13"/>
       <c r="Y356" s="55"/>
       <c r="Z356" s="55"/>
       <c r="AA356" s="55"/>
@@ -18469,8 +18466,8 @@
       <c r="T357" s="13"/>
       <c r="U357" s="13"/>
       <c r="V357" s="13"/>
-      <c r="W357" s="72"/>
-      <c r="X357" s="72"/>
+      <c r="W357" s="13"/>
+      <c r="X357" s="13"/>
       <c r="Y357" s="55"/>
       <c r="Z357" s="55"/>
       <c r="AA357" s="55"/>
@@ -18502,8 +18499,8 @@
       <c r="T358" s="13"/>
       <c r="U358" s="13"/>
       <c r="V358" s="13"/>
-      <c r="W358" s="72"/>
-      <c r="X358" s="72"/>
+      <c r="W358" s="13"/>
+      <c r="X358" s="13"/>
       <c r="Y358" s="55"/>
       <c r="Z358" s="55"/>
       <c r="AA358" s="55"/>
@@ -18535,8 +18532,8 @@
       <c r="T359" s="13"/>
       <c r="U359" s="13"/>
       <c r="V359" s="13"/>
-      <c r="W359" s="72"/>
-      <c r="X359" s="72"/>
+      <c r="W359" s="13"/>
+      <c r="X359" s="13"/>
       <c r="Y359" s="55"/>
       <c r="Z359" s="55"/>
       <c r="AA359" s="55"/>
@@ -18568,8 +18565,8 @@
       <c r="T360" s="13"/>
       <c r="U360" s="13"/>
       <c r="V360" s="13"/>
-      <c r="W360" s="72"/>
-      <c r="X360" s="72"/>
+      <c r="W360" s="13"/>
+      <c r="X360" s="13"/>
       <c r="Y360" s="55"/>
       <c r="Z360" s="55"/>
       <c r="AA360" s="55"/>
@@ -18579,23 +18576,23 @@
       <c r="AC360" s="70"/>
     </row>
     <row r="361" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A361" s="64"/>
-      <c r="B361" s="64"/>
-      <c r="C361" s="64"/>
-      <c r="D361" s="64"/>
-      <c r="E361" s="64"/>
-      <c r="F361" s="64"/>
-      <c r="G361" s="64"/>
+      <c r="A361" s="63"/>
+      <c r="B361" s="63"/>
+      <c r="C361" s="63"/>
+      <c r="D361" s="63"/>
+      <c r="E361" s="63"/>
+      <c r="F361" s="63"/>
+      <c r="G361" s="63"/>
       <c r="H361" s="52"/>
-      <c r="I361" s="64"/>
-      <c r="J361" s="64"/>
-      <c r="K361" s="64"/>
-      <c r="L361" s="64"/>
-      <c r="M361" s="64"/>
-      <c r="N361" s="64"/>
-      <c r="O361" s="64"/>
-      <c r="P361" s="64"/>
-      <c r="Q361" s="64"/>
+      <c r="I361" s="63"/>
+      <c r="J361" s="63"/>
+      <c r="K361" s="63"/>
+      <c r="L361" s="63"/>
+      <c r="M361" s="63"/>
+      <c r="N361" s="63"/>
+      <c r="O361" s="63"/>
+      <c r="P361" s="63"/>
+      <c r="Q361" s="63"/>
       <c r="R361" s="52"/>
       <c r="S361" s="52"/>
       <c r="T361" s="52"/>
@@ -18641,17 +18638,17 @@
     </row>
     <row r="363" spans="1:29" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A363" s="54"/>
-      <c r="B363" s="82" t="s">
+      <c r="B363" s="81" t="s">
         <v>292</v>
       </c>
-      <c r="C363" s="82"/>
-      <c r="D363" s="82"/>
-      <c r="E363" s="82"/>
-      <c r="F363" s="82"/>
+      <c r="C363" s="81"/>
+      <c r="D363" s="81"/>
+      <c r="E363" s="81"/>
+      <c r="F363" s="81"/>
       <c r="G363" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="H363" s="63">
+      <c r="H363" s="62">
         <f>IFERROR(COUNTIFS(L365:L405, "&lt;&gt;", M365:M405, "", N365:N405, "") / COUNTA(L365:L405), 0)</f>
         <v>0</v>
       </c>
@@ -18700,10 +18697,10 @@
         <v>7</v>
       </c>
       <c r="I364" s="54"/>
-      <c r="J364" s="58" t="s">
+      <c r="J364" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="K364" s="59" t="s">
+      <c r="K364" s="58" t="s">
         <v>21</v>
       </c>
       <c r="L364" s="51" t="s">
@@ -18718,41 +18715,41 @@
       <c r="O364" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="P364" s="60" t="s">
+      <c r="P364" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="Q364" s="60" t="s">
+      <c r="Q364" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="R364" s="61" t="s">
+      <c r="R364" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="S364" s="61" t="s">
+      <c r="S364" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="T364" s="61" t="s">
+      <c r="T364" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="U364" s="62" t="s">
+      <c r="U364" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="V364" s="62" t="s">
+      <c r="V364" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="W364" s="61" t="s">
+      <c r="W364" s="60" t="s">
         <v>329</v>
       </c>
-      <c r="X364" s="61"/>
-      <c r="Y364" s="61" t="s">
+      <c r="X364" s="60"/>
+      <c r="Y364" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="Z364" s="61" t="s">
+      <c r="Z364" s="60" t="s">
         <v>313</v>
       </c>
-      <c r="AA364" s="61" t="s">
+      <c r="AA364" s="60" t="s">
         <v>325</v>
       </c>
-      <c r="AB364" s="61" t="s">
+      <c r="AB364" s="60" t="s">
         <v>27</v>
       </c>
       <c r="AC364" s="71" t="s">
@@ -18790,8 +18787,8 @@
       <c r="T365" s="13"/>
       <c r="U365" s="13"/>
       <c r="V365" s="14"/>
-      <c r="W365" s="72"/>
-      <c r="X365" s="72"/>
+      <c r="W365" s="13"/>
+      <c r="X365" s="13"/>
       <c r="Y365" s="55"/>
       <c r="Z365" s="55"/>
       <c r="AA365" s="55"/>
@@ -18823,8 +18820,8 @@
       <c r="T366" s="13"/>
       <c r="U366" s="13"/>
       <c r="V366" s="14"/>
-      <c r="W366" s="72"/>
-      <c r="X366" s="72"/>
+      <c r="W366" s="13"/>
+      <c r="X366" s="13"/>
       <c r="Y366" s="55"/>
       <c r="Z366" s="55"/>
       <c r="AA366" s="55"/>
@@ -18856,8 +18853,8 @@
       <c r="T367" s="13"/>
       <c r="U367" s="13"/>
       <c r="V367" s="14"/>
-      <c r="W367" s="72"/>
-      <c r="X367" s="72"/>
+      <c r="W367" s="13"/>
+      <c r="X367" s="13"/>
       <c r="Y367" s="55"/>
       <c r="Z367" s="55"/>
       <c r="AA367" s="55"/>
@@ -18889,8 +18886,8 @@
       <c r="T368" s="13"/>
       <c r="U368" s="13"/>
       <c r="V368" s="14"/>
-      <c r="W368" s="72"/>
-      <c r="X368" s="72"/>
+      <c r="W368" s="13"/>
+      <c r="X368" s="13"/>
       <c r="Y368" s="55"/>
       <c r="Z368" s="55"/>
       <c r="AA368" s="55"/>
@@ -18922,8 +18919,8 @@
       <c r="T369" s="13"/>
       <c r="U369" s="13"/>
       <c r="V369" s="14"/>
-      <c r="W369" s="72"/>
-      <c r="X369" s="72"/>
+      <c r="W369" s="13"/>
+      <c r="X369" s="13"/>
       <c r="Y369" s="55"/>
       <c r="Z369" s="55"/>
       <c r="AA369" s="55"/>
@@ -18969,8 +18966,8 @@
       <c r="T370" s="13"/>
       <c r="U370" s="13"/>
       <c r="V370" s="14"/>
-      <c r="W370" s="72"/>
-      <c r="X370" s="72"/>
+      <c r="W370" s="13"/>
+      <c r="X370" s="13"/>
       <c r="Y370" s="55"/>
       <c r="Z370" s="55"/>
       <c r="AA370" s="55"/>
@@ -19002,8 +18999,8 @@
       <c r="T371" s="13"/>
       <c r="U371" s="13"/>
       <c r="V371" s="14"/>
-      <c r="W371" s="72"/>
-      <c r="X371" s="72"/>
+      <c r="W371" s="13"/>
+      <c r="X371" s="13"/>
       <c r="Y371" s="55"/>
       <c r="Z371" s="55"/>
       <c r="AA371" s="55"/>
@@ -19035,8 +19032,8 @@
       <c r="T372" s="13"/>
       <c r="U372" s="13"/>
       <c r="V372" s="14"/>
-      <c r="W372" s="72"/>
-      <c r="X372" s="72"/>
+      <c r="W372" s="13"/>
+      <c r="X372" s="13"/>
       <c r="Y372" s="55"/>
       <c r="Z372" s="55"/>
       <c r="AA372" s="55"/>
@@ -19068,8 +19065,8 @@
       <c r="T373" s="13"/>
       <c r="U373" s="13"/>
       <c r="V373" s="14"/>
-      <c r="W373" s="72"/>
-      <c r="X373" s="72"/>
+      <c r="W373" s="13"/>
+      <c r="X373" s="13"/>
       <c r="Y373" s="55"/>
       <c r="Z373" s="55"/>
       <c r="AA373" s="55"/>
@@ -19101,8 +19098,8 @@
       <c r="T374" s="13"/>
       <c r="U374" s="13"/>
       <c r="V374" s="14"/>
-      <c r="W374" s="72"/>
-      <c r="X374" s="72"/>
+      <c r="W374" s="13"/>
+      <c r="X374" s="13"/>
       <c r="Y374" s="55"/>
       <c r="Z374" s="55"/>
       <c r="AA374" s="55"/>
@@ -19148,8 +19145,8 @@
       <c r="T375" s="13"/>
       <c r="U375" s="13"/>
       <c r="V375" s="14"/>
-      <c r="W375" s="72"/>
-      <c r="X375" s="72"/>
+      <c r="W375" s="13"/>
+      <c r="X375" s="13"/>
       <c r="Y375" s="55"/>
       <c r="Z375" s="55"/>
       <c r="AA375" s="55"/>
@@ -19181,8 +19178,8 @@
       <c r="T376" s="13"/>
       <c r="U376" s="13"/>
       <c r="V376" s="14"/>
-      <c r="W376" s="72"/>
-      <c r="X376" s="72"/>
+      <c r="W376" s="13"/>
+      <c r="X376" s="13"/>
       <c r="Y376" s="55"/>
       <c r="Z376" s="55"/>
       <c r="AA376" s="55"/>
@@ -19214,8 +19211,8 @@
       <c r="T377" s="13"/>
       <c r="U377" s="13"/>
       <c r="V377" s="14"/>
-      <c r="W377" s="72"/>
-      <c r="X377" s="72"/>
+      <c r="W377" s="13"/>
+      <c r="X377" s="13"/>
       <c r="Y377" s="55"/>
       <c r="Z377" s="55"/>
       <c r="AA377" s="55"/>
@@ -19247,8 +19244,8 @@
       <c r="T378" s="13"/>
       <c r="U378" s="13"/>
       <c r="V378" s="14"/>
-      <c r="W378" s="72"/>
-      <c r="X378" s="72"/>
+      <c r="W378" s="13"/>
+      <c r="X378" s="13"/>
       <c r="Y378" s="55"/>
       <c r="Z378" s="55"/>
       <c r="AA378" s="55"/>
@@ -19280,8 +19277,8 @@
       <c r="T379" s="13"/>
       <c r="U379" s="13"/>
       <c r="V379" s="14"/>
-      <c r="W379" s="72"/>
-      <c r="X379" s="72"/>
+      <c r="W379" s="13"/>
+      <c r="X379" s="13"/>
       <c r="Y379" s="55"/>
       <c r="Z379" s="55"/>
       <c r="AA379" s="55"/>
@@ -19327,8 +19324,8 @@
       <c r="T380" s="13"/>
       <c r="U380" s="13"/>
       <c r="V380" s="14"/>
-      <c r="W380" s="72"/>
-      <c r="X380" s="72"/>
+      <c r="W380" s="13"/>
+      <c r="X380" s="13"/>
       <c r="Y380" s="55"/>
       <c r="Z380" s="55"/>
       <c r="AA380" s="55"/>
@@ -19360,8 +19357,8 @@
       <c r="T381" s="13"/>
       <c r="U381" s="13"/>
       <c r="V381" s="13"/>
-      <c r="W381" s="72"/>
-      <c r="X381" s="72"/>
+      <c r="W381" s="13"/>
+      <c r="X381" s="13"/>
       <c r="Y381" s="55"/>
       <c r="Z381" s="55"/>
       <c r="AA381" s="55"/>
@@ -19393,8 +19390,8 @@
       <c r="T382" s="13"/>
       <c r="U382" s="13"/>
       <c r="V382" s="13"/>
-      <c r="W382" s="72"/>
-      <c r="X382" s="72"/>
+      <c r="W382" s="13"/>
+      <c r="X382" s="13"/>
       <c r="Y382" s="55"/>
       <c r="Z382" s="55"/>
       <c r="AA382" s="55"/>
@@ -19426,8 +19423,8 @@
       <c r="T383" s="13"/>
       <c r="U383" s="13"/>
       <c r="V383" s="13"/>
-      <c r="W383" s="72"/>
-      <c r="X383" s="72"/>
+      <c r="W383" s="13"/>
+      <c r="X383" s="13"/>
       <c r="Y383" s="55"/>
       <c r="Z383" s="55"/>
       <c r="AA383" s="55"/>
@@ -19459,8 +19456,8 @@
       <c r="T384" s="13"/>
       <c r="U384" s="13"/>
       <c r="V384" s="13"/>
-      <c r="W384" s="72"/>
-      <c r="X384" s="72"/>
+      <c r="W384" s="13"/>
+      <c r="X384" s="13"/>
       <c r="Y384" s="55"/>
       <c r="Z384" s="55"/>
       <c r="AA384" s="55"/>
@@ -19504,8 +19501,8 @@
       <c r="T385" s="13"/>
       <c r="U385" s="13"/>
       <c r="V385" s="13"/>
-      <c r="W385" s="72"/>
-      <c r="X385" s="72"/>
+      <c r="W385" s="13"/>
+      <c r="X385" s="13"/>
       <c r="Y385" s="55"/>
       <c r="Z385" s="55"/>
       <c r="AA385" s="55"/>
@@ -19537,8 +19534,8 @@
       <c r="T386" s="13"/>
       <c r="U386" s="13"/>
       <c r="V386" s="14"/>
-      <c r="W386" s="72"/>
-      <c r="X386" s="72"/>
+      <c r="W386" s="13"/>
+      <c r="X386" s="13"/>
       <c r="Y386" s="55"/>
       <c r="Z386" s="55"/>
       <c r="AA386" s="55"/>
@@ -19570,8 +19567,8 @@
       <c r="T387" s="13"/>
       <c r="U387" s="13"/>
       <c r="V387" s="13"/>
-      <c r="W387" s="72"/>
-      <c r="X387" s="72"/>
+      <c r="W387" s="13"/>
+      <c r="X387" s="13"/>
       <c r="Y387" s="55"/>
       <c r="Z387" s="55"/>
       <c r="AA387" s="55"/>
@@ -19603,8 +19600,8 @@
       <c r="T388" s="13"/>
       <c r="U388" s="13"/>
       <c r="V388" s="13"/>
-      <c r="W388" s="72"/>
-      <c r="X388" s="72"/>
+      <c r="W388" s="13"/>
+      <c r="X388" s="13"/>
       <c r="Y388" s="55"/>
       <c r="Z388" s="55"/>
       <c r="AA388" s="55"/>
@@ -19636,8 +19633,8 @@
       <c r="T389" s="13"/>
       <c r="U389" s="13"/>
       <c r="V389" s="13"/>
-      <c r="W389" s="72"/>
-      <c r="X389" s="72"/>
+      <c r="W389" s="13"/>
+      <c r="X389" s="13"/>
       <c r="Y389" s="55"/>
       <c r="Z389" s="55"/>
       <c r="AA389" s="55"/>
@@ -19669,8 +19666,8 @@
       <c r="T390" s="13"/>
       <c r="U390" s="13"/>
       <c r="V390" s="14"/>
-      <c r="W390" s="72"/>
-      <c r="X390" s="72"/>
+      <c r="W390" s="13"/>
+      <c r="X390" s="13"/>
       <c r="Y390" s="55"/>
       <c r="Z390" s="55"/>
       <c r="AA390" s="55"/>
@@ -19702,8 +19699,8 @@
       <c r="T391" s="13"/>
       <c r="U391" s="13"/>
       <c r="V391" s="13"/>
-      <c r="W391" s="72"/>
-      <c r="X391" s="72"/>
+      <c r="W391" s="13"/>
+      <c r="X391" s="13"/>
       <c r="Y391" s="55"/>
       <c r="Z391" s="55"/>
       <c r="AA391" s="55"/>
@@ -19735,8 +19732,8 @@
       <c r="T392" s="13"/>
       <c r="U392" s="13"/>
       <c r="V392" s="13"/>
-      <c r="W392" s="72"/>
-      <c r="X392" s="72"/>
+      <c r="W392" s="13"/>
+      <c r="X392" s="13"/>
       <c r="Y392" s="55"/>
       <c r="Z392" s="55"/>
       <c r="AA392" s="55"/>
@@ -19768,8 +19765,8 @@
       <c r="T393" s="13"/>
       <c r="U393" s="13"/>
       <c r="V393" s="13"/>
-      <c r="W393" s="72"/>
-      <c r="X393" s="72"/>
+      <c r="W393" s="13"/>
+      <c r="X393" s="13"/>
       <c r="Y393" s="55"/>
       <c r="Z393" s="55"/>
       <c r="AA393" s="55"/>
@@ -19801,8 +19798,8 @@
       <c r="T394" s="13"/>
       <c r="U394" s="13"/>
       <c r="V394" s="13"/>
-      <c r="W394" s="72"/>
-      <c r="X394" s="72"/>
+      <c r="W394" s="13"/>
+      <c r="X394" s="13"/>
       <c r="Y394" s="55"/>
       <c r="Z394" s="55"/>
       <c r="AA394" s="55"/>
@@ -19813,15 +19810,15 @@
     </row>
     <row r="395" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A395" s="54"/>
-      <c r="B395" s="73" t="s">
+      <c r="B395" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="C395" s="74"/>
-      <c r="D395" s="74"/>
-      <c r="E395" s="74"/>
-      <c r="F395" s="74"/>
-      <c r="G395" s="74"/>
-      <c r="H395" s="75"/>
+      <c r="C395" s="73"/>
+      <c r="D395" s="73"/>
+      <c r="E395" s="73"/>
+      <c r="F395" s="73"/>
+      <c r="G395" s="73"/>
+      <c r="H395" s="74"/>
       <c r="I395" s="54"/>
       <c r="J395" s="9"/>
       <c r="K395" s="10"/>
@@ -19836,8 +19833,8 @@
       <c r="T395" s="13"/>
       <c r="U395" s="13"/>
       <c r="V395" s="13"/>
-      <c r="W395" s="72"/>
-      <c r="X395" s="72"/>
+      <c r="W395" s="13"/>
+      <c r="X395" s="13"/>
       <c r="Y395" s="55"/>
       <c r="Z395" s="55"/>
       <c r="AA395" s="55"/>
@@ -19848,13 +19845,13 @@
     </row>
     <row r="396" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A396" s="54"/>
-      <c r="B396" s="76"/>
-      <c r="C396" s="77"/>
-      <c r="D396" s="77"/>
-      <c r="E396" s="77"/>
-      <c r="F396" s="77"/>
-      <c r="G396" s="77"/>
-      <c r="H396" s="78"/>
+      <c r="B396" s="75"/>
+      <c r="C396" s="76"/>
+      <c r="D396" s="76"/>
+      <c r="E396" s="76"/>
+      <c r="F396" s="76"/>
+      <c r="G396" s="76"/>
+      <c r="H396" s="77"/>
       <c r="I396" s="54"/>
       <c r="J396" s="9"/>
       <c r="K396" s="10"/>
@@ -19869,8 +19866,8 @@
       <c r="T396" s="13"/>
       <c r="U396" s="13"/>
       <c r="V396" s="13"/>
-      <c r="W396" s="72"/>
-      <c r="X396" s="72"/>
+      <c r="W396" s="13"/>
+      <c r="X396" s="13"/>
       <c r="Y396" s="55"/>
       <c r="Z396" s="55"/>
       <c r="AA396" s="55"/>
@@ -19881,13 +19878,13 @@
     </row>
     <row r="397" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A397" s="54"/>
-      <c r="B397" s="76"/>
-      <c r="C397" s="77"/>
-      <c r="D397" s="77"/>
-      <c r="E397" s="77"/>
-      <c r="F397" s="77"/>
-      <c r="G397" s="77"/>
-      <c r="H397" s="78"/>
+      <c r="B397" s="75"/>
+      <c r="C397" s="76"/>
+      <c r="D397" s="76"/>
+      <c r="E397" s="76"/>
+      <c r="F397" s="76"/>
+      <c r="G397" s="76"/>
+      <c r="H397" s="77"/>
       <c r="I397" s="54"/>
       <c r="J397" s="9"/>
       <c r="K397" s="10"/>
@@ -19902,8 +19899,8 @@
       <c r="T397" s="13"/>
       <c r="U397" s="13"/>
       <c r="V397" s="13"/>
-      <c r="W397" s="72"/>
-      <c r="X397" s="72"/>
+      <c r="W397" s="13"/>
+      <c r="X397" s="13"/>
       <c r="Y397" s="55"/>
       <c r="Z397" s="55"/>
       <c r="AA397" s="55"/>
@@ -19914,13 +19911,13 @@
     </row>
     <row r="398" spans="1:29" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A398" s="54"/>
-      <c r="B398" s="79"/>
-      <c r="C398" s="80"/>
-      <c r="D398" s="80"/>
-      <c r="E398" s="80"/>
-      <c r="F398" s="80"/>
-      <c r="G398" s="80"/>
-      <c r="H398" s="81"/>
+      <c r="B398" s="78"/>
+      <c r="C398" s="79"/>
+      <c r="D398" s="79"/>
+      <c r="E398" s="79"/>
+      <c r="F398" s="79"/>
+      <c r="G398" s="79"/>
+      <c r="H398" s="80"/>
       <c r="I398" s="54"/>
       <c r="J398" s="9"/>
       <c r="K398" s="10"/>
@@ -19935,8 +19932,8 @@
       <c r="T398" s="13"/>
       <c r="U398" s="13"/>
       <c r="V398" s="13"/>
-      <c r="W398" s="72"/>
-      <c r="X398" s="72"/>
+      <c r="W398" s="13"/>
+      <c r="X398" s="13"/>
       <c r="Y398" s="55"/>
       <c r="Z398" s="55"/>
       <c r="AA398" s="55"/>
@@ -19968,8 +19965,8 @@
       <c r="T399" s="13"/>
       <c r="U399" s="13"/>
       <c r="V399" s="13"/>
-      <c r="W399" s="72"/>
-      <c r="X399" s="72"/>
+      <c r="W399" s="13"/>
+      <c r="X399" s="13"/>
       <c r="Y399" s="55"/>
       <c r="Z399" s="55"/>
       <c r="AA399" s="55"/>
@@ -20001,8 +19998,8 @@
       <c r="T400" s="13"/>
       <c r="U400" s="13"/>
       <c r="V400" s="13"/>
-      <c r="W400" s="72"/>
-      <c r="X400" s="72"/>
+      <c r="W400" s="13"/>
+      <c r="X400" s="13"/>
       <c r="Y400" s="55"/>
       <c r="Z400" s="55"/>
       <c r="AA400" s="55"/>
@@ -20034,8 +20031,8 @@
       <c r="T401" s="13"/>
       <c r="U401" s="13"/>
       <c r="V401" s="13"/>
-      <c r="W401" s="72"/>
-      <c r="X401" s="72"/>
+      <c r="W401" s="13"/>
+      <c r="X401" s="13"/>
       <c r="Y401" s="55"/>
       <c r="Z401" s="55"/>
       <c r="AA401" s="55"/>
@@ -20067,8 +20064,8 @@
       <c r="T402" s="13"/>
       <c r="U402" s="13"/>
       <c r="V402" s="13"/>
-      <c r="W402" s="72"/>
-      <c r="X402" s="72"/>
+      <c r="W402" s="13"/>
+      <c r="X402" s="13"/>
       <c r="Y402" s="55"/>
       <c r="Z402" s="55"/>
       <c r="AA402" s="55"/>
@@ -20100,8 +20097,8 @@
       <c r="T403" s="13"/>
       <c r="U403" s="13"/>
       <c r="V403" s="13"/>
-      <c r="W403" s="72"/>
-      <c r="X403" s="72"/>
+      <c r="W403" s="13"/>
+      <c r="X403" s="13"/>
       <c r="Y403" s="55"/>
       <c r="Z403" s="55"/>
       <c r="AA403" s="55"/>
@@ -20133,8 +20130,8 @@
       <c r="T404" s="13"/>
       <c r="U404" s="13"/>
       <c r="V404" s="13"/>
-      <c r="W404" s="72"/>
-      <c r="X404" s="72"/>
+      <c r="W404" s="13"/>
+      <c r="X404" s="13"/>
       <c r="Y404" s="55"/>
       <c r="Z404" s="55"/>
       <c r="AA404" s="55"/>
@@ -20166,8 +20163,8 @@
       <c r="T405" s="13"/>
       <c r="U405" s="13"/>
       <c r="V405" s="13"/>
-      <c r="W405" s="72"/>
-      <c r="X405" s="72"/>
+      <c r="W405" s="13"/>
+      <c r="X405" s="13"/>
       <c r="Y405" s="55"/>
       <c r="Z405" s="55"/>
       <c r="AA405" s="55"/>
@@ -20177,23 +20174,23 @@
       <c r="AC405" s="70"/>
     </row>
     <row r="406" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A406" s="64"/>
-      <c r="B406" s="64"/>
-      <c r="C406" s="64"/>
-      <c r="D406" s="64"/>
-      <c r="E406" s="64"/>
-      <c r="F406" s="64"/>
-      <c r="G406" s="64"/>
+      <c r="A406" s="63"/>
+      <c r="B406" s="63"/>
+      <c r="C406" s="63"/>
+      <c r="D406" s="63"/>
+      <c r="E406" s="63"/>
+      <c r="F406" s="63"/>
+      <c r="G406" s="63"/>
       <c r="H406" s="52"/>
-      <c r="I406" s="64"/>
-      <c r="J406" s="64"/>
-      <c r="K406" s="64"/>
-      <c r="L406" s="64"/>
-      <c r="M406" s="64"/>
-      <c r="N406" s="64"/>
-      <c r="O406" s="64"/>
-      <c r="P406" s="64"/>
-      <c r="Q406" s="64"/>
+      <c r="I406" s="63"/>
+      <c r="J406" s="63"/>
+      <c r="K406" s="63"/>
+      <c r="L406" s="63"/>
+      <c r="M406" s="63"/>
+      <c r="N406" s="63"/>
+      <c r="O406" s="63"/>
+      <c r="P406" s="63"/>
+      <c r="Q406" s="63"/>
       <c r="R406" s="52"/>
       <c r="S406" s="52"/>
       <c r="T406" s="52"/>

--- a/스케쥴 시트/★★이게진짜 Daily 종합사이트 스케줄★★.xlsx
+++ b/스케쥴 시트/★★이게진짜 Daily 종합사이트 스케줄★★.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\정동교\문서 자동화 TEST\커서 바이브코딩 자동화 관련\스케쥴 시트\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6462421D-C65C-4718-BF6F-8E96A09809ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B692B4-6B8E-44A1-946F-FE3114189269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2256,11 +2256,11 @@
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2901,15 +2901,15 @@
     </row>
     <row r="2" spans="1:28" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="54"/>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
       <c r="I2" s="54"/>
       <c r="J2" s="54"/>
       <c r="K2" s="54"/>
@@ -5307,15 +5307,15 @@
     </row>
     <row r="49" spans="1:28" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="54"/>
-      <c r="B49" s="82" t="s">
+      <c r="B49" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="C49" s="82"/>
-      <c r="D49" s="82"/>
-      <c r="E49" s="82"/>
-      <c r="F49" s="82"/>
-      <c r="G49" s="82"/>
-      <c r="H49" s="82"/>
+      <c r="C49" s="81"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
       <c r="I49" s="54"/>
       <c r="J49" s="54"/>
       <c r="K49" s="54"/>
@@ -7593,13 +7593,13 @@
     </row>
     <row r="92" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="54"/>
-      <c r="B92" s="81" t="s">
+      <c r="B92" s="82" t="s">
         <v>137</v>
       </c>
-      <c r="C92" s="81"/>
-      <c r="D92" s="81"/>
-      <c r="E92" s="81"/>
-      <c r="F92" s="81"/>
+      <c r="C92" s="82"/>
+      <c r="D92" s="82"/>
+      <c r="E92" s="82"/>
+      <c r="F92" s="82"/>
       <c r="G92" s="47" t="s">
         <v>289</v>
       </c>
@@ -9948,13 +9948,13 @@
     </row>
     <row r="138" spans="1:29" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="54"/>
-      <c r="B138" s="81" t="s">
+      <c r="B138" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="C138" s="81"/>
-      <c r="D138" s="81"/>
-      <c r="E138" s="81"/>
-      <c r="F138" s="81"/>
+      <c r="C138" s="82"/>
+      <c r="D138" s="82"/>
+      <c r="E138" s="82"/>
+      <c r="F138" s="82"/>
       <c r="G138" s="47" t="s">
         <v>289</v>
       </c>
@@ -12176,13 +12176,13 @@
     </row>
     <row r="183" spans="1:29" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="54"/>
-      <c r="B183" s="81" t="s">
+      <c r="B183" s="82" t="s">
         <v>260</v>
       </c>
-      <c r="C183" s="81"/>
-      <c r="D183" s="81"/>
-      <c r="E183" s="81"/>
-      <c r="F183" s="81"/>
+      <c r="C183" s="82"/>
+      <c r="D183" s="82"/>
+      <c r="E183" s="82"/>
+      <c r="F183" s="82"/>
       <c r="G183" s="47" t="s">
         <v>289</v>
       </c>
@@ -13848,13 +13848,13 @@
     </row>
     <row r="228" spans="1:29" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="54"/>
-      <c r="B228" s="81" t="s">
+      <c r="B228" s="82" t="s">
         <v>259</v>
       </c>
-      <c r="C228" s="81"/>
-      <c r="D228" s="81"/>
-      <c r="E228" s="81"/>
-      <c r="F228" s="81"/>
+      <c r="C228" s="82"/>
+      <c r="D228" s="82"/>
+      <c r="E228" s="82"/>
+      <c r="F228" s="82"/>
       <c r="G228" s="47" t="s">
         <v>289</v>
       </c>
@@ -15444,13 +15444,13 @@
     </row>
     <row r="273" spans="1:29" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" s="54"/>
-      <c r="B273" s="81" t="s">
+      <c r="B273" s="82" t="s">
         <v>290</v>
       </c>
-      <c r="C273" s="81"/>
-      <c r="D273" s="81"/>
-      <c r="E273" s="81"/>
-      <c r="F273" s="81"/>
+      <c r="C273" s="82"/>
+      <c r="D273" s="82"/>
+      <c r="E273" s="82"/>
+      <c r="F273" s="82"/>
       <c r="G273" s="47" t="s">
         <v>289</v>
       </c>
@@ -17042,13 +17042,13 @@
     </row>
     <row r="318" spans="1:29" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A318" s="54"/>
-      <c r="B318" s="81" t="s">
+      <c r="B318" s="82" t="s">
         <v>291</v>
       </c>
-      <c r="C318" s="81"/>
-      <c r="D318" s="81"/>
-      <c r="E318" s="81"/>
-      <c r="F318" s="81"/>
+      <c r="C318" s="82"/>
+      <c r="D318" s="82"/>
+      <c r="E318" s="82"/>
+      <c r="F318" s="82"/>
       <c r="G318" s="47" t="s">
         <v>289</v>
       </c>
@@ -18638,13 +18638,13 @@
     </row>
     <row r="363" spans="1:29" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A363" s="54"/>
-      <c r="B363" s="81" t="s">
+      <c r="B363" s="82" t="s">
         <v>292</v>
       </c>
-      <c r="C363" s="81"/>
-      <c r="D363" s="81"/>
-      <c r="E363" s="81"/>
-      <c r="F363" s="81"/>
+      <c r="C363" s="82"/>
+      <c r="D363" s="82"/>
+      <c r="E363" s="82"/>
+      <c r="F363" s="82"/>
       <c r="G363" s="47" t="s">
         <v>289</v>
       </c>
@@ -21676,24 +21676,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B395:H398"/>
+    <mergeCell ref="B273:F273"/>
+    <mergeCell ref="B305:H308"/>
+    <mergeCell ref="B318:F318"/>
+    <mergeCell ref="B350:H353"/>
+    <mergeCell ref="B363:F363"/>
+    <mergeCell ref="B215:H218"/>
+    <mergeCell ref="B260:H263"/>
+    <mergeCell ref="B170:H173"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B228:F228"/>
     <mergeCell ref="B124:H127"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B34:H37"/>
     <mergeCell ref="B49:H49"/>
     <mergeCell ref="B81:H84"/>
     <mergeCell ref="B92:F92"/>
-    <mergeCell ref="B215:H218"/>
-    <mergeCell ref="B260:H263"/>
-    <mergeCell ref="B170:H173"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B228:F228"/>
-    <mergeCell ref="B395:H398"/>
-    <mergeCell ref="B273:F273"/>
-    <mergeCell ref="B305:H308"/>
-    <mergeCell ref="B318:F318"/>
-    <mergeCell ref="B350:H353"/>
-    <mergeCell ref="B363:F363"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J93:K93 J139:K139 J184:K184 J229:K229">

--- a/스케쥴 시트/★★이게진짜 Daily 종합사이트 스케줄★★.xlsx
+++ b/스케쥴 시트/★★이게진짜 Daily 종합사이트 스케줄★★.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\정동교\문서 자동화 TEST\커서 바이브코딩 자동화 관련\스케쥴 시트\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B692B4-6B8E-44A1-946F-FE3114189269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E35E9A-7272-41AE-A408-483CA3937DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="341">
   <si>
     <t>종합사이트 스케줄표 (11월)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1398,9 +1398,6 @@
   <si>
     <t>1호기</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>완료</t>
   </si>
 </sst>
 </file>
@@ -12438,9 +12435,7 @@
       <c r="AB186" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="AC186" s="70" t="s">
-        <v>341</v>
-      </c>
+      <c r="AC186" s="70"/>
     </row>
     <row r="187" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A187" s="54"/>

--- a/스케쥴 시트/★★이게진짜 Daily 종합사이트 스케줄★★.xlsx
+++ b/스케쥴 시트/★★이게진짜 Daily 종합사이트 스케줄★★.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\정동교\문서 자동화 TEST\커서 바이브코딩 자동화 관련\스케쥴 시트\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E35E9A-7272-41AE-A408-483CA3937DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8278E7-7912-4AE7-9D87-02E84B20AD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
